--- a/客户分类结果.xlsx
+++ b/客户分类结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$C$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,12 +480,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,6 +505,11 @@
           <t>二级分类</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>三级分类</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -521,6 +527,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -538,6 +549,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>政策性银行</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -555,6 +571,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -572,6 +593,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -589,6 +615,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -606,6 +637,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -623,6 +659,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -640,6 +681,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -657,6 +703,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>商业银行分行</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -674,6 +725,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>城市商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -691,6 +747,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -708,6 +769,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>城市商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -725,6 +791,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>城市商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -742,6 +813,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -759,6 +835,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -776,6 +857,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -793,6 +879,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>政策性银行</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -810,6 +901,11 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -827,11 +923,16 @@
           <t>券商</t>
         </is>
       </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>东证融汇证券资产管理有限公司</t>
+          <t>五矿证券有限公司</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -842,13 +943,18 @@
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -859,13 +965,18 @@
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -876,13 +987,18 @@
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信证券股份有限公司辽宁分公司</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -893,13 +1009,18 @@
       <c r="C24" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司辽宁分公司</t>
+          <t>中信证券股份有限公司内蒙古分公司</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -910,13 +1031,18 @@
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司内蒙古分公司</t>
+          <t>中原证券股份有限公司</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -927,13 +1053,18 @@
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>中原证券股份有限公司</t>
+          <t>中天国富证券有限公司</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -944,13 +1075,18 @@
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>中天国富证券有限公司</t>
+          <t>中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -961,13 +1097,18 @@
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -978,13 +1119,18 @@
       <c r="C29" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>中航证券有限公司</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -995,13 +1141,18 @@
       <c r="C30" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>中航证券有限公司</t>
+          <t>中金公司</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1012,13 +1163,18 @@
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>中金公司</t>
+          <t>中金财富证券有限公司</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1029,13 +1185,18 @@
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>中金财富证券有限公司</t>
+          <t>信达证券股份有限公司</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1046,13 +1207,18 @@
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>信达证券股份有限公司</t>
+          <t>华泰证券股份有限公司</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1063,13 +1229,18 @@
       <c r="C34" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>兴证证券资产管理有限公司</t>
+          <t>华安证券股份有限公司</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1080,13 +1251,18 @@
       <c r="C35" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>华泰证券股份有限公司</t>
+          <t>华融证券股份有限公司</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1097,13 +1273,18 @@
       <c r="C36" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>华安证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1114,13 +1295,18 @@
       <c r="C37" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>华融证券股份有限公司</t>
+          <t>国泰君安证券股份有限公司</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1131,13 +1317,18 @@
       <c r="C38" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>国金证券股份有限公司</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1148,13 +1339,18 @@
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>国泰君安证券股份有限公司</t>
+          <t>国元证券股份有限公司</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1165,13 +1361,18 @@
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司</t>
+          <t>国联证券股份有限公司</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1182,13 +1383,18 @@
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司</t>
+          <t>国海证券股份有限公司</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1199,13 +1405,18 @@
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>国联证券股份有限公司</t>
+          <t>国都证券股份有限公司</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1216,13 +1427,18 @@
       <c r="C43" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>国海证券股份有限公司</t>
+          <t>天风证券股份有限公司</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1233,13 +1449,18 @@
       <c r="C44" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>国都证券股份有限公司</t>
+          <t>安信证券股份有限公司</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1250,13 +1471,18 @@
       <c r="C45" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
+          <t>开源证券股份有限公司</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1267,13 +1493,18 @@
       <c r="C46" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>安信证券股份有限公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1284,13 +1515,18 @@
       <c r="C47" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1301,13 +1537,18 @@
       <c r="C48" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
+          <t>海通证券股份有限公司</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1318,13 +1559,18 @@
       <c r="C49" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>瑞银证券有限责任公司</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1335,13 +1581,18 @@
       <c r="C50" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>外资券商</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>海通证券股份有限公司</t>
+          <t>申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1352,13 +1603,18 @@
       <c r="C51" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>瑞银证券有限责任公司</t>
+          <t>第一创业证券股份有限公司</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1369,13 +1625,18 @@
       <c r="C52" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司</t>
+          <t>西部证券股份有限公司</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1386,13 +1647,18 @@
       <c r="C53" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>第一创业证券股份有限公司</t>
+          <t>银河证券</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1403,13 +1669,18 @@
       <c r="C54" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
+          <t>摩根士丹利</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1420,13 +1691,18 @@
       <c r="C55" s="3" t="inlineStr">
         <is>
           <t>券商</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>外资券商</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>银河证券</t>
+          <t>中信期货有限公司</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -1436,14 +1712,19 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>摩根士丹利</t>
+          <t>冠通期货股份有限公司</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -1453,14 +1734,19 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>中信期货有限公司</t>
+          <t>华泰期货有限公司</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -1471,13 +1757,18 @@
       <c r="C58" s="3" t="inlineStr">
         <is>
           <t>期货</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>冠通期货股份有限公司</t>
+          <t>南华期货股份有限公司</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -1488,13 +1779,18 @@
       <c r="C59" s="3" t="inlineStr">
         <is>
           <t>期货</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司</t>
+          <t>中金基金管理有限公司</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -1504,14 +1800,19 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>南华期货股份有限公司</t>
+          <t>华安基金管理有限公司</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -1521,14 +1822,19 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>中金基金管理有限公司</t>
+          <t>华夏基金管理有限公司</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -1539,13 +1845,18 @@
       <c r="C62" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>华安基金管理有限公司</t>
+          <t>博时基金管理有限公司</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -1556,13 +1867,18 @@
       <c r="C63" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>华夏基金管理有限公司</t>
+          <t>工银瑞信基金管理有限公司</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -1573,13 +1889,18 @@
       <c r="C64" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>博时基金管理有限公司</t>
+          <t>建信基金管理有限公司</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -1590,13 +1911,18 @@
       <c r="C65" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>工银瑞信基金管理有限公司</t>
+          <t>易方达基金管理有限公司</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -1607,13 +1933,18 @@
       <c r="C66" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>建信基金管理有限公司</t>
+          <t>东证融汇证券资产管理有限公司</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -1624,13 +1955,18 @@
       <c r="C67" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>易方达基金管理有限公司</t>
+          <t>兴证证券资产管理有限公司</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -1641,6 +1977,11 @@
       <c r="C68" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
         </is>
       </c>
     </row>
@@ -1660,6 +2001,11 @@
           <t>基金</t>
         </is>
       </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1677,6 +2023,11 @@
           <t>基金</t>
         </is>
       </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1694,6 +2045,11 @@
           <t>基金</t>
         </is>
       </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1711,11 +2067,16 @@
           <t>基金</t>
         </is>
       </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>中信资本控股有限公司</t>
+          <t>中信资本股权投资管理有限公司</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -1726,13 +2087,18 @@
       <c r="C73" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>中信资本股权投资管理有限公司</t>
+          <t>中投保信投资管理有限公司</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -1743,13 +2109,18 @@
       <c r="C74" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>中国银河投资管理有限公司</t>
+          <t>凯雷（北京）投资管理有限公司</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -1760,13 +2131,18 @@
       <c r="C75" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>中投保信投资管理有限公司</t>
+          <t>上海微策金融信息服务有限公司</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -1777,13 +2153,18 @@
       <c r="C76" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>中融国际信托有限公司</t>
+          <t>中信资本控股有限公司</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -1794,13 +2175,18 @@
       <c r="C77" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>凯雷（北京）投资管理有限公司</t>
+          <t>中国银河投资管理有限公司</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -1811,13 +2197,18 @@
       <c r="C78" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>宜信</t>
+          <t>中融国际信托有限公司</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -1828,13 +2219,18 @@
       <c r="C79" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>上海微策金融信息服务有限公司</t>
+          <t>宜信</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -1845,6 +2241,11 @@
       <c r="C80" s="3" t="inlineStr">
         <is>
           <t>基金</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
         </is>
       </c>
     </row>
@@ -1864,6 +2265,11 @@
           <t>融资租赁</t>
         </is>
       </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -1881,6 +2287,11 @@
           <t>融资租赁</t>
         </is>
       </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -1898,6 +2309,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -1915,6 +2331,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -1932,6 +2353,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1949,6 +2375,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -1966,6 +2397,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -1983,6 +2419,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2000,6 +2441,11 @@
           <t>保险</t>
         </is>
       </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2017,6 +2463,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2034,6 +2481,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2051,6 +2499,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2068,6 +2517,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2085,6 +2535,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2102,6 +2553,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2119,6 +2571,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2136,6 +2589,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2153,6 +2607,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2170,6 +2625,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2187,6 +2643,7 @@
           <t>采矿业</t>
         </is>
       </c>
+      <c r="D100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2204,6 +2661,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2221,6 +2679,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2238,6 +2697,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2255,6 +2715,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2272,6 +2733,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2289,6 +2751,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2306,6 +2769,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2323,6 +2787,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2340,6 +2805,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2357,6 +2823,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2374,6 +2841,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2391,6 +2859,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2408,6 +2877,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2425,6 +2895,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2442,6 +2913,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2459,6 +2931,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2476,6 +2949,7 @@
           <t>制造业</t>
         </is>
       </c>
+      <c r="D117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2493,6 +2967,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2510,6 +2985,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2527,6 +3003,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -2544,6 +3021,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -2561,6 +3039,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -2578,6 +3057,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -2595,6 +3075,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -2612,6 +3093,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -2629,6 +3111,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -2646,6 +3129,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -2663,6 +3147,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -2680,6 +3165,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -2697,6 +3183,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -2714,6 +3201,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -2731,6 +3219,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -2748,6 +3237,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -2765,6 +3255,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -2782,6 +3273,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -2799,6 +3291,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -2816,6 +3309,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -2833,6 +3327,7 @@
           <t>服务业</t>
         </is>
       </c>
+      <c r="D138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -2850,6 +3345,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -2867,6 +3363,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -2884,6 +3381,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -2901,6 +3399,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -2918,6 +3417,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -2935,6 +3435,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -2952,6 +3453,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -2969,6 +3471,7 @@
           <t>建筑业</t>
         </is>
       </c>
+      <c r="D146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -2986,6 +3489,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3003,6 +3507,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3020,6 +3525,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3037,6 +3543,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3054,6 +3561,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -3071,6 +3579,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -3088,6 +3597,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -3105,6 +3615,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -3122,6 +3633,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -3139,6 +3651,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -3156,6 +3669,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -3173,6 +3687,7 @@
           <t>贸易业</t>
         </is>
       </c>
+      <c r="D158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -3190,6 +3705,7 @@
           <t>其他</t>
         </is>
       </c>
+      <c r="D159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -3207,6 +3723,7 @@
           <t>个人客户</t>
         </is>
       </c>
+      <c r="D160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -3224,6 +3741,7 @@
           <t>个人客户</t>
         </is>
       </c>
+      <c r="D161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -3241,6 +3759,7 @@
           <t>个人客户</t>
         </is>
       </c>
+      <c r="D162" s="5" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -3258,6 +3777,7 @@
           <t>其他</t>
         </is>
       </c>
+      <c r="D163" s="6" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -3275,9 +3795,10 @@
           <t>其他</t>
         </is>
       </c>
+      <c r="D164" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C164"/>
+  <autoFilter ref="A1:D164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3292,7 +3813,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -3361,12 +3882,12 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>一级分类</t>
+          <t>二级分类</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>二级分类</t>
+          <t>三级分类</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -3378,211 +3899,211 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>个人客户</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>个人客户</t>
+          <t>保险集团</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>产业客户</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>外资券商</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>产业客户</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>证券公司</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>产业客户</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>证券公司分公司</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>产业客户</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>产业客户</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>券商私募（另类投资）</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>产业客户</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>采矿业</t>
+          <t>私募基金</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>私募投资集团</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>期货公司</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>商业银行分行</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市商业银行</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>政策性银行</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/客户分类结果.xlsx
+++ b/客户分类结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$348</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,17 +52,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E5E8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCF3CF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D335"/>
+  <dimension ref="A1:D348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -528,65 +528,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KPX CHEMICAL CO., LTD</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>MPG Operations LLC</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Qube Research &amp; Technologies Limited</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>Mitsubishi Corporation RtM International Pte.Ltd.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SamsungC&amp;T Corporation</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>Qube Research &amp; Technologies Limited</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TCL中环新能源科技股份有限公司</t>
+          <t>SamsungC&amp;T Corporation</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -604,29 +604,25 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>citadel advisors singapore pte limited</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>TCL中环新能源科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>三棵树涂料股份有限公司</t>
+          <t>万华化学集团股份有限公司</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -644,7 +640,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>三维控股集团股份有限公司</t>
+          <t>三棵树涂料股份有限公司</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -654,7 +650,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -662,86 +658,82 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海东方证券资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>券商私募（另类投资）</t>
-        </is>
-      </c>
+          <t>三维控股集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>上海东证期货有限公司</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>上海东方证券资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海健顺投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>上海东证期货有限公司</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海半夏投资管理中心（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+          <t>上海健顺投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>基金</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>私募基金</t>
         </is>
@@ -750,25 +742,29 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海卓然工程技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+          <t>上海半夏投资管理中心（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海吉家宠物食品有限公司</t>
+          <t>上海卓然工程技术股份有限公司</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -778,7 +774,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -786,7 +782,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>上海妙可蓝多食品科技股份有限公司</t>
+          <t>上海吉家宠物食品有限公司</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -804,179 +800,171 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海旭冕投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海墨襄数据科技有限公司</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海期货交易所</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>期货交易所</t>
-        </is>
-      </c>
+          <t>上海妙可蓝多食品科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海期货交易所商品二部-红桃三</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>期货交易所</t>
+          <t>上海旭冕投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>上海泓湖私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>上海期货交易所</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>期货交易所</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>上海洛书投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>上海期货交易所商品二部-红桃三</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>期货交易所</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>上海牛伞私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海来伊份股份有限公司</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>上海璞泰来新能源科技集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
+          <t>上海泓湖私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>上海申银万国证券研究所有限公司</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>证券研究所</t>
+          <t>上海洛书投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>上海电气集团国控环球工程有限公司</t>
+          <t>上海溯智信息科技有限公司</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -986,7 +974,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -994,320 +982,308 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>上海盘京投资管理中心（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海璞泰来新能源科技集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海聊塑私募基金管理中心（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>上海申银万国证券研究所有限公司</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>证券研究所</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>上海蝶威私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海电气集团国控环球工程有限公司</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>上海赛科石油化工有限责任公司</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+          <t>上海盘京投资管理中心（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>东兴期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>上海聊塑私募基金管理中心（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>东北证券股份有限公司上海证券研究咨询分公司</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
-        </is>
-      </c>
+          <t>上海赛科石油化工有限责任公司</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>东兴期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>东方财富证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+          <t>东北证券股份有限公司上海证券研究咨询分公司</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>东莞南玻太阳能玻璃有限公司</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
+          <t>东方证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>东方财富证券股份有限公司</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>个人客户</t>
+          <t>金融客户</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>个人客户</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>个人客户</t>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>东莞南玻太阳能玻璃有限公司</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>东马油脂（张家港保税区）有限公司</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>中信建投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>中信建投资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>中信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
+          <t>中信建投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>期货公司</t>
         </is>
@@ -1316,113 +1292,117 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>中信建投资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司 北京</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
+          <t>中信期货有限公司</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司东营分行</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>商业银行分行</t>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司乌鲁木齐分行</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>商业银行分行</t>
+          <t>中信证券股份有限公司 北京</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>中化国际（控股）股份有限公司</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
+          <t>中信银行股份有限公司东营分行</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>商业银行分行</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>中化能源股份有限公司</t>
+          <t>中化国际（控股）股份有限公司</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1440,7 +1420,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>中化资本数字科技有限公司</t>
+          <t>中化能源股份有限公司</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1450,7 +1430,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1458,51 +1438,47 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>中原证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>中化资本数字科技有限公司</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>中国农业发展银行</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>政策性银行</t>
+          <t>中原证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>中国化学工程第三建设有限公司</t>
+          <t>中哲物产集团有限公司</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1512,7 +1488,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1520,7 +1496,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>中国化工经济技术发展中心</t>
+          <t>中国中材集团有限公司</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1530,7 +1506,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1538,29 +1514,29 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>中国农业发展银行</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>政策性银行</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>中国寰球工程有限公司</t>
+          <t>中国化工经济技术发展中心</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1570,7 +1546,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1578,65 +1554,69 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>中国巨石股份有限公司</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
+          <t>中国化工资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>中国平安保险（集团）股份有限公司</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>保险集团</t>
+          <t>中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>中国期货市场监控中心有限责任公司</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr"/>
+          <t>中国天辰工程有限公司</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>中国海洋石油集团有限公司</t>
+          <t>中国寰球工程有限公司</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -1646,7 +1626,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>采矿业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1654,7 +1634,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>中国石化上海石油化工股份有限公司</t>
+          <t>中国巨石股份有限公司</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -1672,43 +1652,47 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>中国石化化工销售有限公司</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr"/>
+          <t>中国平安保险（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>中国石化工程建设有限公司</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr"/>
+          <t>中国期货市场监控中心有限责任公司</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>中国石化集团经济技术研究院有限公司</t>
+          <t>中国海洋石油集团有限公司</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -1718,7 +1702,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>采矿业</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1726,29 +1710,25 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>中国石化集团资本有限公司</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
+          <t>中国石化上海石油化工股份有限公司</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>中国石油化工股份有限公司大连石油化工研究院</t>
+          <t>中国石化化工销售有限公司</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -1758,7 +1738,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
@@ -1766,7 +1746,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>中国石油天然气股份有限公司华东化工销售分公司</t>
+          <t>中国石化工程建设有限公司</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -1776,7 +1756,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1784,7 +1764,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>中国石油天然气股份有限公司吉林石化分公司</t>
+          <t>中国石化集团经济技术研究院有限公司</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -1794,7 +1774,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1802,25 +1782,29 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>中国石油天然气股份有限公司大连石化分公司</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr"/>
+          <t>中国石化集团资本有限公司</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>中国石油集团经济技术研究院</t>
+          <t>中国石油化工股份有限公司大连石油化工研究院</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -1838,7 +1822,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>中国神华煤制油化工有限公司</t>
+          <t>中国石油天然气股份有限公司华东化工销售分公司</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -1848,7 +1832,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -1856,7 +1840,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>中国纸业投资有限公司</t>
+          <t>中国石油天然气股份有限公司吉林石化分公司</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -1874,29 +1858,25 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>中国石油天然气股份有限公司大连石化分公司</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>中國石油化學工業開發股份有限公司</t>
+          <t>中国石油集团经济技术研究院</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -1906,7 +1886,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -1914,7 +1894,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>中基宁波集团股份有限公司</t>
+          <t>中国神华煤制油化工有限公司</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -1924,7 +1904,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -1932,47 +1912,47 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>中安鼎盛（深圳）私募证券投资基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>中国纸业投资有限公司</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>中山市皓东化工有限公司</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr"/>
+          <t>中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>中材科技风电叶片股份有限公司</t>
+          <t>中國石油化學工業開發股份有限公司</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -1990,87 +1970,91 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>中欧基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>公募基金</t>
-        </is>
-      </c>
+          <t>中基宁波集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>中欧基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>中海油能源经济咨询有限公司</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr"/>
+          <t>中泰证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>中石化上海工程有限公司</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr"/>
+          <t>中泰证券股份有限公司淄博分公司</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>中石化宁波镇海炼化有限公司</t>
+          <t>中海油能源经济咨询有限公司</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2080,7 +2064,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -2088,7 +2072,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>中石化洛阳工程有限公司</t>
+          <t>中石化上海工程有限公司</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2106,7 +2090,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>中石化湖南石油化工有限公司</t>
+          <t>中石化宁波镇海炼化有限公司</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2124,7 +2108,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>中石化石油化工科学研究院有限公司</t>
+          <t>中石化洛阳工程有限公司</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2134,7 +2118,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
@@ -2142,7 +2126,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>中石油华东设计院有限公司</t>
+          <t>中石化湖南石油化工有限公司</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2152,7 +2136,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -2160,7 +2144,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>中科合成油工程有限公司</t>
+          <t>中石化石油化工科学研究院有限公司</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2170,7 +2154,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
@@ -2178,7 +2162,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>中粮嘉华实业有限公司</t>
+          <t>中石油华东设计院有限公司</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2188,7 +2172,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2196,47 +2180,43 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>中银国际期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>中科合成油工程有限公司</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>中间市场部</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
+          <t>中粮信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>乐金化学（中国）投资有限公司</t>
+          <t>中粮嘉华实业有限公司</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -2246,7 +2226,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
@@ -2254,7 +2234,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>乐高商贸（深圳）有限公司</t>
+          <t>中粮家佳康（湖北）有限公司</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2264,7 +2244,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
@@ -2272,61 +2252,69 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>书赞桉诺（上海）贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr"/>
+          <t>中粮期货有限公司</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>云南云天化石化有限公司</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr"/>
+          <t>中银国际期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>云南交发云翼科技有限公司</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr"/>
+          <t>中间市场部</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>云南磷化集团有限公司</t>
+          <t>乐金化学（中国）投资有限公司</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -2336,7 +2324,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>采矿业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
@@ -2344,7 +2332,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>云南磷化集团海口磷业有限公司</t>
+          <t>书赞桉诺（上海）贸易有限公司</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -2354,7 +2342,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>采矿业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -2362,29 +2350,25 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>交银施罗德基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>公募基金</t>
-        </is>
-      </c>
+          <t>云南云天化石化有限公司</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>亨氏（中国）投资有限公司</t>
+          <t>云南交发云翼科技有限公司</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -2394,7 +2378,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -2402,25 +2386,25 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>以化投资有限公司</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr"/>
+          <t>云南磷化集团有限公司</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>采矿业</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>伊士曼（中国）投资管理有限公司</t>
+          <t>云南磷化集团海口磷业有限公司</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -2430,7 +2414,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>采矿业</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
@@ -2438,25 +2422,29 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>伯恩光学（惠州）有限公司</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr"/>
+          <t>交银施罗德基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>公募基金</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>佛山市顺德区巴德富实业有限公司</t>
+          <t>亨氏（中国）投资有限公司</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -2474,29 +2462,25 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>信达证券股份有限公司</t>
+          <t>以化投资有限公司</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>倍舒特（天津）卫生用品有限公司</t>
+          <t>伊士曼（中国）投资管理有限公司</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -2514,149 +2498,149 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>元大期貨股份有限公司-台中分公司</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>佛山市伟德纺织有限公司</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>元胜投资管理（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>佛山市顺德区巴德富实业有限公司</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司北京分公司</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
+          <t>信达证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>克拉玛依市富城能源集团有限公司</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>采矿业</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr"/>
+          <t>元大期貨股份有限公司-台中分公司</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>兴业经济研究咨询股份有限公司</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr"/>
+          <t>元胜投资管理（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>兄弟科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>内蒙古伊利实业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr"/>
+          <t>光大证券股份有限公司北京分公司</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>内蒙古蒙牛乳业（集团）股份有限公司</t>
+          <t>克拉玛依市富城能源集团有限公司</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -2666,7 +2650,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>采矿业</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr"/>
@@ -2674,7 +2658,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>农夫山泉股份有限公司</t>
+          <t>兴业经济研究咨询股份有限公司</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -2684,7 +2668,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr"/>
@@ -2692,25 +2676,29 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>凯威尔树脂</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr"/>
+          <t>兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>凯莱英医药集团（天津）股份有限公司</t>
+          <t>内蒙古蒙牛乳业（集团）股份有限公司</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -2728,29 +2716,25 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>前海开源基金管理有限公司</t>
+          <t>农业农村部大数据发展中心</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>公募基金</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>北京三快在线科技有限公司</t>
+          <t>农夫山泉股份有限公司</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -2760,7 +2744,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr"/>
@@ -2768,7 +2752,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>北京中基亚太贸易有限公司</t>
+          <t>凯威尔树脂</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -2778,7 +2762,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr"/>
@@ -2786,7 +2770,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>北京云杉世界信息技术集团有限公司</t>
+          <t>凯莱英医药集团（天津）股份有限公司</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -2796,7 +2780,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr"/>
@@ -2804,51 +2788,47 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>北京凯瑞加投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
+          <t>前海开源基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>基金</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>公募基金</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>北京橙色印象资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>北京三快在线科技有限公司</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>北京王小卤网络科技有限公司</t>
+          <t>北京中基亚太贸易有限公司</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -2858,7 +2838,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr"/>
@@ -2866,7 +2846,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>北京百麦食品加工有限公司</t>
+          <t>北京云杉世界信息技术集团有限公司</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -2876,7 +2856,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr"/>
@@ -2884,43 +2864,51 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>北京睿谷嘉业贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr"/>
+          <t>北京凯瑞加投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>北京石油化工工程有限公司</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr"/>
+          <t>北京橙色印象资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>北京福田戴姆勒汽车有限公司</t>
+          <t>北京百麦食品加工有限公司</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -2938,176 +2926,160 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>北京秋收私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>北京睿谷嘉业贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>北京鸿道投资管理有限责任公司</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>北京石油化工工程有限公司</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>华安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>北京福田戴姆勒汽车有限公司</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>北京秋收私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司上海人民路营业部</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>华夏云食（深圳）科技有限公司</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>华福证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>华泰期货有限公司</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>华融金融租赁股份有限公司</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>金融租赁</t>
+          <t>华福证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>华西证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>华融金融租赁股份有限公司</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>金融租赁</t>
         </is>
       </c>
     </row>
@@ -3117,17 +3089,17 @@
           <t>华西证券股份有限公司</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>证券公司</t>
         </is>
@@ -3136,20 +3108,20 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
+          <t>华西证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>证券公司</t>
         </is>
@@ -3161,17 +3133,17 @@
           <t>华闻期货有限公司</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>期货公司</t>
         </is>
@@ -3198,7 +3170,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>南京诚志清洁能源有限公司</t>
+          <t>卓创资讯公共</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -3208,7 +3180,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr"/>
@@ -3219,17 +3191,17 @@
           <t>南华期货股份有限公司</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>期货公司</t>
         </is>
@@ -3238,20 +3210,24 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>南宁乐飞网络科技有限责任公司</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr"/>
+          <t>南方基金管理股份有限公司</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>公募基金</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3274,7 +3250,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>合肥市裕同印刷包装有限公司</t>
+          <t>厦门国贸农林有限公司</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -3284,7 +3260,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
@@ -3292,7 +3268,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>嘉吉投资（中国）有限公司</t>
+          <t>双乐颜料股份有限公司</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -3302,7 +3278,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
@@ -3310,7 +3286,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>四川东树新材料有限公司上海分公司</t>
+          <t>台塑工业（宁波）有限公司</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -3328,7 +3304,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>四川德康农牧食品集团股份有限公司</t>
+          <t>嘉吉投资（中国）有限公司</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -3338,7 +3314,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr"/>
@@ -3346,7 +3322,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>四川水井坊股份有限公司</t>
+          <t>四川东树新材料有限公司上海分公司</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -3364,7 +3340,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>固始县蓼源加油站</t>
+          <t>四川剑南春（集团）有限责任公司</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -3374,7 +3350,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr"/>
@@ -3382,108 +3358,96 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>四川德康农牧食品集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>国投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>四川水井坊股份有限公司</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>国泰君安期货有限公司</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>国家能源集团科学技术研究院有限公司</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>国海良时期货有限公司</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
+          <t>国投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
         <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>期货公司</t>
         </is>
@@ -3492,126 +3456,126 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>国海证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>国泰君安期货有限公司</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>国电投未来能源发展（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr"/>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>国盛证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>国海良时期货有限公司</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>国联期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>国海证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>国联民生证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>国电投未来能源发展（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>国联民生证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
+          <t>国盛证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>证券公司</t>
         </is>
@@ -3620,20 +3584,20 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>国贸期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
+          <t>国联期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
         <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>期货公司</t>
         </is>
@@ -3642,105 +3606,113 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司上海投资咨询分公司</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
+          <t>国联民生证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>圆信永丰基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>公募基金</t>
+          <t>国联民生证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>國票金融控股股份有限公司</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr"/>
+          <t>国贸期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>圣奥化学科技有限公司</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr"/>
+          <t>国金证券股份有限公司上海投资咨询分公司</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>圣莱科特精细化工（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr"/>
+          <t>國票金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>塞拉尼斯（中国）投资有限公司</t>
+          <t>圣奥化学科技有限公司</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -3758,109 +3730,109 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>大连商品交易所</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
+          <t>圣莱科特精细化工（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>天弘基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>公募基金</t>
-        </is>
-      </c>
+          <t>塞拉尼斯（中国）投资有限公司</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司海南研究咨询分公司</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
+          <t>大地期货有限公司</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>奥胜制造（太仓）有限公司</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr"/>
+          <t>大连商品交易所</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>奥镁（中国）有限公司</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr"/>
+          <t>天风证券股份有限公司海南研究咨询分公司</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>威士伯（上海）企业管理有限公司</t>
+          <t>奥胜制造（太仓）有限公司</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -3870,7 +3842,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr"/>
@@ -3878,159 +3850,159 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>宁波灵均投资管理合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>威士伯（上海）企业管理有限公司</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>安庆高新技术产业开发区管理委员会</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr"/>
+          <t>宁夏宝廷新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>安德里茨（中国）有限公司</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr"/>
+          <t>宁波灵均投资管理合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>安德里茨（中国）有限公司</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>宝武清洁能源有限公司</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr"/>
+          <t>宏源期货有限公司</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>富宝账号维护</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
+          <t>宝武清洁能源有限公司</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr"/>
+      <c r="D177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>富海集团新能源控股有限公司</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
+          <t>富宝客户</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr"/>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>富瑞金融集团香港有限公司</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
+          <t>富宝账号维护</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C179" s="4" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr"/>
+      <c r="D179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>小山前农业（威海）集团有限公司</t>
+          <t>富海集团新能源控股有限公司</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -4040,7 +4012,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr"/>
@@ -4048,7 +4020,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>山东东明石化集团有限公司</t>
+          <t>山东万达化工有限公司</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -4066,7 +4038,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>山东产权交易集团有限公司</t>
+          <t>山东京博石油化工有限公司</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -4076,7 +4048,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr"/>
@@ -4084,7 +4056,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>山东京博石油化工有限公司</t>
+          <t>山东卓创资讯股份有限公司</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -4094,7 +4066,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr"/>
@@ -4156,7 +4128,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>山东海科化工有限公司</t>
+          <t>山东宏桥新型材料有限公司</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -4174,47 +4146,43 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东海科化工有限公司</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>山西阳光焦化集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr"/>
+          <t>山东省农业发展信贷担保有限责任公司</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>巨星农牧有限公司</t>
+          <t>山东祖豪物流有限公司</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -4224,7 +4192,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr"/>
@@ -4232,29 +4200,25 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>巨杉（上海）资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>山东美佳集团有限公司</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>常州优通精细化学有限公司</t>
+          <t>山东裕龙石化有限公司</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -4272,7 +4236,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>常州市化工轻工材料总公司</t>
+          <t>山西阳光焦化集团股份有限公司</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -4282,7 +4246,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr"/>
@@ -4290,7 +4254,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>广东三津食品有限公司</t>
+          <t>岳阳兴长石化股份有限公司</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -4308,65 +4272,69 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>广东凌丰集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr"/>
+          <t>工银瑞信基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>公募基金</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>广东厚方投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D196" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>巨星农牧有限公司</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>广东宇新能源科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr"/>
+          <t>巨杉（上海）资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>广东海大集团股份有限公司</t>
+          <t>帝斯曼芬美意营养品（上海）有限公司</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -4376,7 +4344,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr"/>
@@ -4384,7 +4352,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>广东温氏南方家禽育种有限公司</t>
+          <t>常州优通精细化学有限公司</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -4394,7 +4362,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
@@ -4402,7 +4370,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>广东百味佳味业科技股份有限公司</t>
+          <t>常州市化工轻工材料总公司</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -4412,7 +4380,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
@@ -4420,7 +4388,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>广东福百盛股份有限公司</t>
+          <t>广东三津食品有限公司</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -4438,7 +4406,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>广东远东高分子科技有限公司</t>
+          <t>广东凌丰集团股份有限公司</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -4456,69 +4424,69 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>广发期货有限公司</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>广东厚方投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
-        </is>
-      </c>
+          <t>广东宇新能源科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>广州久昊能源有限公司</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr"/>
+          <t>广东德汇投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>广州南顺清洁用品有限公司</t>
+          <t>广东海大集团股份有限公司</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -4528,7 +4496,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr"/>
@@ -4536,7 +4504,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>广州恒越日用化工贸易有限公司</t>
+          <t>广东温氏南方家禽育种有限公司</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -4546,7 +4514,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr"/>
@@ -4554,7 +4522,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>广州慕可生物科技有限公司</t>
+          <t>广东百味佳味业科技股份有限公司</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -4572,29 +4540,25 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>广州期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>广东福百盛股份有限公司</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>康佳集团股份有限公司</t>
+          <t>广东远东高分子科技有限公司</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -4612,20 +4576,20 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>建信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
+          <t>广发期货有限公司</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
         <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D211" s="4" t="inlineStr">
+      <c r="D211" s="5" t="inlineStr">
         <is>
           <t>期货公司</t>
         </is>
@@ -4634,20 +4598,20 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
+          <t>广发证券股份有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
         <is>
           <t>券商</t>
         </is>
       </c>
-      <c r="D212" s="4" t="inlineStr">
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>证券公司分公司</t>
         </is>
@@ -4656,51 +4620,43 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>德邦证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D213" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>广州久昊能源有限公司</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>思致投资（海南）有限公司</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广州南顺清洁用品有限公司</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>惠生工程（中国）有限公司</t>
+          <t>广州市森大贸易有限公司</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -4710,7 +4666,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr"/>
@@ -4718,7 +4674,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>成都云图控股股份有限公司</t>
+          <t>广州恒越日用化工贸易有限公司</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -4728,7 +4684,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr"/>
@@ -4736,7 +4692,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>成都劳恩普斯科技有限公司</t>
+          <t>广州慕可生物科技有限公司</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -4746,7 +4702,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr"/>
@@ -4754,185 +4710,193 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="D218" s="4" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
+          <t>广州慕可生物科技有限公司</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>摩根士丹利基金管理（中国）有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D219" s="4" t="inlineStr">
-        <is>
-          <t>公募基金</t>
+          <t>广州期货交易所股份有限公司</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>期货交易所</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>摩科瑞（中国）金属资源有限公司</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr"/>
+          <t>广州期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>方正中期期货有限公司</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>广西路桥工程集团有限公司</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>方正证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D222" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>康佳集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>无锡市丛榕化工产品有限公司</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="inlineStr"/>
+          <t>建信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>无锡茂偌贸易咨询服务有限公司</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr"/>
+          <t>建信金融资产投资有限公司</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>旭阳营销有限公司</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr"/>
+          <t>开源证券股份有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>昆明天牧农产品有限公司</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr"/>
+          <t>思致投资（海南）有限公司</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>昊华化工有限责任公司</t>
+          <t>惠生工程（中国）有限公司</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -4942,7 +4906,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
@@ -4950,7 +4914,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>李锦记（新会）食品有限公司</t>
+          <t>成都云图控股股份有限公司</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -4968,7 +4932,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>杭州朝霞实业有限公司</t>
+          <t>成都劳恩普斯科技有限公司</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -4978,7 +4942,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr"/>
@@ -4986,29 +4950,25 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>杭州润洲私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>成都南玻玻璃有限公司</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>榆林中科洁净能源创新研究院</t>
+          <t>成都天府乡村发展集团有限公司</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -5018,7 +4978,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr"/>
@@ -5026,123 +4986,131 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>正大投资股份有限公司</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="inlineStr"/>
+          <t>招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>武汉凯泰兴建筑装饰工程有限公司</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr"/>
+          <t>摩根士丹利基金管理（中国）有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>公募基金</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>永安国富资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D234" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>摩科瑞（中国）金属资源有限公司</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>永安期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D235" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>新疆天业股份有限公司</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>江苏扬农化工集团有限公司</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C236" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="inlineStr"/>
+          <t>方正中期期货有限公司</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>江苏盐城源耀饲料有限公司</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr"/>
+          <t>方正证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>江西省农业科学院农产品加工研究所</t>
+          <t>施耐德电气（中国）有限公司</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -5152,7 +5120,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
@@ -5160,7 +5128,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>沃森氏（威海）农牧发展有限公司</t>
+          <t>无锡市丛榕化工产品有限公司</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -5170,7 +5138,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr"/>
@@ -5178,7 +5146,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>河北万展星科技有限公司</t>
+          <t>无锡茂偌贸易咨询服务有限公司</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -5196,7 +5164,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>河南心连心化学工业集团股份有限公司</t>
+          <t>旭阳营销有限公司</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -5206,7 +5174,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr"/>
@@ -5214,29 +5182,25 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>泰康资产管理有限责任公司</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>保险资管</t>
-        </is>
-      </c>
+          <t>昆明天牧农产品有限公司</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>洽洽食品股份有限公司</t>
+          <t>昊华化工有限责任公司</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -5254,7 +5218,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>浙商中拓集团股份有限公司</t>
+          <t>曲靖市沾益区德方纳米科技有限公司</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -5264,7 +5228,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr"/>
@@ -5272,51 +5236,47 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>浙商期货有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>李锦记（新会）食品有限公司</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>杭州润洲私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>浙江乘龙钢结构有限公司</t>
+          <t>柘城县恒康超市</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -5326,7 +5286,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
@@ -5334,105 +5294,109 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>采矿业</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr"/>
+          <t>格林大华期货有限公司</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>浙江朗裔资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D249" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>正大投资股份有限公司</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>浙江杭实善成实业有限公司</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr"/>
+          <t>永安国富资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>浙江汇丰设备租赁有限公司</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr"/>
+          <t>永安期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>浙江浙银金融租赁股份有限公司</t>
-        </is>
-      </c>
-      <c r="B252" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="D252" s="4" t="inlineStr">
-        <is>
-          <t>金融租赁</t>
-        </is>
-      </c>
+          <t>江苏扬农化工集团有限公司</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>浙江菜鸟供应链管理有限公司</t>
+          <t>江苏盐城源耀饲料有限公司</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -5442,7 +5406,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
@@ -5450,29 +5414,25 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>浙江金榕树投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B254" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D254" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>江苏苏博特新材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>浦林成山（山东）轮胎有限公司</t>
+          <t>江西省农业科学院农产品加工研究所</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -5482,7 +5442,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
@@ -5490,153 +5450,145 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>海南时代共赢私募基金管理合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>河北万展星科技有限公司</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>海南盛冠达私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>河南心连心化学工业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>海南赛尔私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>泰康资产管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>保险资管</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>海通期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>洽洽食品股份有限公司</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>深圳信立泰药业股份有限公司</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="inlineStr"/>
+          <t>浙商期货有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>深圳光大同创新材料股份有限公司</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D261" s="3" t="inlineStr"/>
+          <t>浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>深圳市凯丰投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D262" s="4" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>浙江信汇新材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>深圳市北领科技物流有限公司</t>
+          <t>浙江卫星化学实业有限公司</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -5646,7 +5598,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
@@ -5654,7 +5606,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>深圳市裕同包装科技股份有限公司</t>
+          <t>浙江杭实善成实业有限公司</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -5664,7 +5616,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
@@ -5672,7 +5624,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>深圳市财富趋势科技股份有限公司</t>
+          <t>浙江汇丰设备租赁有限公司</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -5690,97 +5642,113 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>温氏食品集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D266" s="3" t="inlineStr"/>
+          <t>浙江省国有资本运营有限公司</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>湖北劲牌保健酒业有限公司</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="inlineStr"/>
+          <t>浙江金榕树投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>湖南盟盟国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D268" s="3" t="inlineStr"/>
+          <t>海南大学</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>滨化集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr"/>
+          <t>海南时代共赢私募基金管理合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>烟台中宠食品股份有限公司</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="inlineStr"/>
+          <t>海通期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>物产中大化工集团有限公司</t>
+          <t>淄博旭欧贸易有限公司</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -5798,7 +5766,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>玛氏箭牌糖果（中国）有限公司</t>
+          <t>深圳TCL新技术有限公司</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -5816,7 +5784,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>玛氏食品（北京）有限公司</t>
+          <t>深圳光大同创新材料股份有限公司</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -5834,25 +5802,29 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>现代牧业（集团）有限公司</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="inlineStr"/>
+          <t>深圳市凯丰投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>皮埃西（上海）农业科技有限公司</t>
+          <t>深圳市裕同包装科技股份有限公司</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -5862,7 +5834,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
@@ -5870,7 +5842,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>盈德气体（上海）有限公司</t>
+          <t>深圳市财富趋势科技股份有限公司</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -5880,7 +5852,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr"/>
@@ -5888,7 +5860,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>益海嘉里金龙鱼食品集团股份有限公司</t>
+          <t>温氏食品集团股份有限公司</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -5898,7 +5870,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
@@ -5906,7 +5878,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>石油和化学工业规划院</t>
+          <t>湖北劲牌保健酒业有限公司</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -5916,7 +5888,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
@@ -5924,7 +5896,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>确信乐思化学（上海）有限公司</t>
+          <t>湖南盟盟国际贸易有限公司</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -5934,7 +5906,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
@@ -5942,7 +5914,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>神华工程技术有限公司安徽分公司</t>
+          <t>湖南麻辣王子食品有限公司</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -5952,7 +5924,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
@@ -5960,7 +5932,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>福建联合石油化工有限公司</t>
+          <t>滨化集团股份有限公司</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -5978,7 +5950,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>科氏晟腾贸易（上海）有限公司</t>
+          <t>烟台中宠食品股份有限公司</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -5988,7 +5960,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
@@ -5996,7 +5968,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>秦皇岛天鼎化工有限公司</t>
+          <t>物产中大化工集团有限公司</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -6006,7 +5978,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr"/>
@@ -6014,7 +5986,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>立华彩印（昆山）有限公司</t>
+          <t>玛氏箭牌糖果（中国）有限公司</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -6032,29 +6004,25 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>紫金天风期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B285" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D285" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>现代牧业（集团）有限公司</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>统一企业（中国）投资有限公司</t>
+          <t>珠海小志投教科技有限公司</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -6064,7 +6032,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
@@ -6072,7 +6040,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>美乐家（中国）日用品有限公司</t>
+          <t>盈德气体（上海）有限公司</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -6082,7 +6050,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
@@ -6090,7 +6058,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>联合利华（中国）有限公司</t>
+          <t>益海嘉里金龙鱼食品集团股份有限公司</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -6108,43 +6076,47 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>联想（深圳）电子有限公司</t>
-        </is>
-      </c>
-      <c r="B289" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C289" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D289" s="3" t="inlineStr"/>
+          <t>石景涛</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D289" s="6" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>股票</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C290" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D290" s="6" t="inlineStr"/>
+          <t>石油和化学工业规划院</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>臺灣塑膠工業股份有限公司</t>
+          <t>确信乐思化学（上海）有限公司</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -6162,7 +6134,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>艾仕得涂料系统（上海）有限公司</t>
+          <t>神华工程技术有限公司安徽分公司</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -6172,7 +6144,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
@@ -6180,7 +6152,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>苏州富士莱医药股份有限公司</t>
+          <t>福建联合石油化工有限公司</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -6198,7 +6170,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>苏州市恒顺纸塑有限公司</t>
+          <t>科氏晟腾贸易（上海）有限公司</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -6208,7 +6180,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
@@ -6216,7 +6188,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>荣盛石化销售有限公司</t>
+          <t>秦皇岛天鼎化工有限公司</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -6226,7 +6198,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
@@ -6234,7 +6206,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>荷美尔（中国）投资有限公司</t>
+          <t>立华彩印（昆山）有限公司</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -6252,25 +6224,29 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>西南化工研究设计院有限公司</t>
-        </is>
-      </c>
-      <c r="B297" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C297" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D297" s="3" t="inlineStr"/>
+          <t>紫金天风期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>西安禾丰饲料科技有限公司</t>
+          <t>统一企业（中国）投资有限公司</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -6280,7 +6256,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
@@ -6288,7 +6264,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>西安陕鼓动力股份有限公司</t>
+          <t>美乐家（中国）日用品有限公司</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -6298,7 +6274,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
@@ -6306,29 +6282,25 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D300" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>联合利华（中国）有限公司</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>诺维信（中国）投资有限公司</t>
+          <t>联想（深圳）电子有限公司</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -6346,73 +6318,61 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>贝莱德资产管理北亚有限公司</t>
-        </is>
-      </c>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C302" s="4" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D302" s="4" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
+          <t>肇庆市哈力化工有限公司</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>财达证券股份有限公司</t>
+          <t>股票</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D303" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B304" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C304" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D304" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>臺灣塑膠工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>辽宁省粮食发展集团有限责任公司</t>
+          <t>艾仕得涂料系统（上海）有限公司</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -6422,7 +6382,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
@@ -6430,7 +6390,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>达利食品集团有限公司</t>
+          <t>苏州富士莱医药股份有限公司</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -6448,7 +6408,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>达能（中国）食品饮料有限公司</t>
+          <t>苏州市恒顺纸塑有限公司</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -6466,29 +6426,25 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司</t>
-        </is>
-      </c>
-      <c r="B308" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C308" s="4" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
+          <t>荣盛石化销售有限公司</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>郑州全新食品有限公司</t>
+          <t>荷美尔（中国）投资有限公司</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -6506,29 +6462,25 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>郑州商品交易所</t>
+          <t>营销管理部</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>金融客户</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="D310" s="4" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>重庆天旭化工有限公司</t>
+          <t>西安禾丰饲料科技有限公司</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -6538,7 +6490,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr"/>
@@ -6546,7 +6498,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>重庆富源化工有限公司</t>
+          <t>西安陕鼓动力股份有限公司</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -6564,25 +6516,29 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>重庆市化工研究院有限公司</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C313" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D313" s="3" t="inlineStr"/>
+          <t>西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>重庆百亚卫生用品股份有限公司</t>
+          <t>诚泰信息科技（天津）有限公司</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -6592,7 +6548,7 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr"/>
@@ -6600,7 +6556,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>重庆金科房地产开发有限公司</t>
+          <t>诺维信（中国）投资有限公司</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -6610,7 +6566,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr"/>
@@ -6618,61 +6574,73 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>重庆（荣昌）生猪大数据中心</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C316" s="3" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr"/>
+          <t>贝莱德资产管理北亚有限公司</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>金发科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C317" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D317" s="3" t="inlineStr"/>
+          <t>财达证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>金能科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="B318" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C318" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D318" s="3" t="inlineStr"/>
+          <t>财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>铁骑力士食品有限责任公司</t>
+          <t>达利食品集团有限公司</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
@@ -6682,7 +6650,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr"/>
@@ -6690,47 +6658,47 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>银河期货有限公司</t>
-        </is>
-      </c>
-      <c r="B320" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C320" s="4" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D320" s="4" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>达能（中国）食品饮料有限公司</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>销售事业部</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr"/>
+          <t>远东国际融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>长兴化学工业（中国）有限公司</t>
+          <t>郑州全新食品有限公司</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -6748,73 +6716,65 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D323" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>郑州商品交易所</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>商品交易所</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B324" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C324" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D324" s="4" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
-        </is>
-      </c>
+          <t>重庆富源化工有限公司</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B325" s="4" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C325" s="4" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D325" s="4" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>重庆市化工研究院有限公司</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>长鑫科技集团股份有限公司</t>
+          <t>重庆百亚卫生用品股份有限公司</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -6832,7 +6792,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>陕西化工集团有限公司</t>
+          <t>重庆金科房地产开发有限公司</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
@@ -6842,7 +6802,7 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr"/>
@@ -6850,7 +6810,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>陕西外经贸化工有限公司</t>
+          <t>重庆（荣昌）生猪大数据中心</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -6860,7 +6820,7 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr"/>
@@ -6868,7 +6828,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>陕西延长石油（集团）有限责任公司</t>
+          <t>金发科技股份有限公司</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
@@ -6878,7 +6838,7 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>采矿业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr"/>
@@ -6886,7 +6846,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>隆基绿能科技股份有限公司</t>
+          <t>金能科技股份有限公司</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -6904,7 +6864,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>青岛海大生物集团股份有限公司</t>
+          <t>铁骑力士食品有限责任公司</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
@@ -6914,7 +6874,7 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr"/>
@@ -6922,25 +6882,29 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>青岛瑞金发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C332" s="3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D332" s="3" t="inlineStr"/>
+          <t>银河期货有限公司</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>青岛驿达天下物流有限公司</t>
+          <t>长兴化学工业（中国）有限公司</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
@@ -6950,7 +6914,7 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr"/>
@@ -6958,41 +6922,287 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>青岛鼎信通讯股份有限公司</t>
-        </is>
-      </c>
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C334" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D334" s="3" t="inlineStr"/>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
+          <t>长城证券股份有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>证券公司分公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>长江证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D336" s="5" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>陕西化工集团有限公司</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>陕西外经贸化工有限公司</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>陕西延长石油（集团）有限责任公司</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>采矿业</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>隆基绿能科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>青岛中际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>青岛海大生物集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>青岛驿达天下物流有限公司</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>青岛鼎信通讯股份有限公司</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
           <t>顶峰油脂化工（泰兴）有限公司</t>
         </is>
       </c>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C335" s="3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D335" s="3" t="inlineStr"/>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>鲁西化工集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>鹏欣环球资源股份有限公司</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>采矿业</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>齐鲁制药有限公司</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D335"/>
+  <autoFilter ref="A1:D348"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7003,7 +7213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7025,7 +7235,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -7035,7 +7245,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
@@ -7055,7 +7265,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -7065,294 +7275,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>三级</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>保险资管</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>保险集团</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>证券公司分公司</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>证券研究所</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>商品交易所</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>期货交易所</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>公募基金</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>券商私募（另类投资）</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金融租赁</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>商业银行分行</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>政策性银行</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/客户分类结果.xlsx
+++ b/客户分类结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$344</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$329</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D344"/>
+  <dimension ref="A1:D329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上海东证期货有限公司</t>
+          <t>一德期货有限公司</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>上海中期期货股份有限公司</t>
+          <t>上海东证期货有限公司</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>上海众壹资产管理有限公司</t>
+          <t>上海东证期货有限公司江苏分公司</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -564,19 +564,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>上海信超投资管理有限公司</t>
+          <t>上海中期期货股份有限公司</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -586,19 +586,19 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海八桂资产管理有限公司</t>
+          <t>上海众壹资产管理有限公司</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -620,25 +620,29 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上海冕泓实业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
+          <t>上海信超投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海双隆投资有限公司</t>
+          <t>上海八桂资产管理有限公司</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -660,65 +664,69 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海品责资产管理中心（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海冕泓实业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海岐源石油化工有限公司</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>上海双隆投资有限公司</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>上海巨侠网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
+          <t>上海文谛资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海市申辰律师事务所</t>
+          <t>上海河清龙樾企业管理有限公司</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -736,7 +744,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海德直税务师事务所有限公司</t>
+          <t>上海港耀科技有限公司</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -754,47 +762,47 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海德贝私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海申袆实业有限公司</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海悦祺雅文化传播有限公司</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
+          <t>上海申银万国证券研究所有限公司</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>证券研究所</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>上海敢响企业管理咨询有限公司</t>
+          <t>上海礼上东振实业有限公司</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -804,7 +812,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
@@ -812,7 +820,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海文谛资产管理有限公司</t>
+          <t>上海维万私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -834,7 +842,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海服指商务咨询有限公司</t>
+          <t>上海翔涌化工国际贸易有限公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -852,43 +860,51 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海河清龙樾企业管理有限公司</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+          <t>上海西部永唐投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>上海泛询供应链管理有限公司</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>上海远澜私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>上海港耀科技有限公司</t>
+          <t>上海金沐岑科技发展有限公司</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -906,7 +922,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>上海申银万国证券研究所有限公司</t>
+          <t>上海魔寓私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -916,19 +932,19 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>证券研究所</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>上海礼上东振实业有限公司</t>
+          <t>东方龙木（海南）国际贸易有限公司</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -946,220 +962,240 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>上海维万私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>东莞市大岭山赣进粮油经营部</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>上海美顺广告设计有限公司</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>上海翔涌化工国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海西部永唐投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>上海远澜私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>上海魔寓私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>东方新科（大连）商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>东方龙木（海南）国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>东海资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>东莞市大岭山赣进粮油经营部</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>东莞市鑫铭鲜食品供应链有限公司</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2044,7 +2080,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -2066,7 +2102,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -2088,7 +2124,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -2110,7 +2146,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -2132,7 +2168,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -2154,7 +2190,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -2176,7 +2212,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -3144,7 +3180,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个体期货</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -3166,293 +3202,269 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中信建投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中信期货有限公司</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中原期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中国平安保险（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中基宁波集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中央储备粮辽东湾直属库有限公司</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中泰期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中粮农业产业管理服务有限公司</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中粮期货有限公司</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中衍期货有限公司</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中间市场部</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>临清市翔茂木材加工厂</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>个体期货</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>云南程鹏饲料有限责任公司</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>中信建投期货有限公司</t>
+          <t>五矿期货有限公司</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -3474,87 +3486,83 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>中信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>产品管理部</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>中原期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>元氏县炜淼农业开发有限公司</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>中哲物产集团有限公司</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr"/>
+          <t>光大期货有限公司</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>中国供销集团延长果业有限责任公司</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr"/>
+          <t>全国畜牧总站</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>中国平安保险（集团）股份有限公司</t>
+          <t>兴业期货有限公司</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -3564,55 +3572,63 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>保险集团</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>中基宁波集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr"/>
+          <t>兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>中基宁波集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr"/>
+          <t>兴证期货有限公司</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>中效河北农牧有限公司</t>
+          <t>冀交港口物流唐山有限公司</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -3622,7 +3638,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3630,207 +3646,199 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>中泰期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>冠县乐园养殖有限公司</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>中粮农业产业管理服务有限公司</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr"/>
+          <t>刘晓明</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>中粮期货有限公司</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京六合粮源农业科技有限公司</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>中衍期货有限公司</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京国康未来医学研究院</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>中间市场部</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
+          <t>北京摩卡站餐饮管理有限公司</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>云南程鹏饲料有限责任公司</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>北京星鹏联海私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>云财富期货有限公司</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京永盛芳科贸有限公司</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>五矿期货有限公司</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京盛维弘波管理顾问有限公司</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>产品管理部</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
+          <t>北京顶峰时刻科技有限公司</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>产品管理部</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr"/>
+          <t>华安期货有限责任公司青岛营业部</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>光大期货有限公司</t>
+          <t>华泰期货有限公司</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -3852,7 +3860,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>兴业期货有限公司</t>
+          <t>华泰期货有限公司上海世纪大道营业部</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -3867,36 +3875,32 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>华裕农业科技有限公司</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>兴证期货有限公司</t>
+          <t>华闻期货有限公司</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -3918,7 +3922,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>冀交港口物流唐山有限公司</t>
+          <t>南京洲利盛科技有限公司</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -3936,7 +3940,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>北京中深能源有限公司</t>
+          <t>南宁市荣泽钢材有限公司</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -3954,47 +3958,51 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>北京悟源资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>南志云</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>北京摩卡站餐饮管理有限公司</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr"/>
+          <t>南通中睿投资有限公司</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>北京永盛芳科贸有限公司</t>
+          <t>南通市崇川区帅昌贸易有限公司</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -4012,7 +4020,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>北京盛维弘波管理顾问有限公司</t>
+          <t>南通鸿华化工有限公司</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -4022,7 +4030,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr"/>
@@ -4030,91 +4038,83 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>博白县那林镇多福养鸡专业合作社</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司上海世纪大道营业部</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>合肥神之手贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>华闻期货有限公司</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>吉林普康农业有限公司</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>南京千亿家畜牧有限公司</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr"/>
+          <t>周琎</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>南京源素新材料有限公司</t>
+          <t>呼伦贝尔上丰管道有限公司</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -4132,73 +4132,61 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>南华期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>哈尔滨领骏商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>南华期货股份有限公司上海虹桥路营业部</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>唐人神集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>南通中睿投资有限公司</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>唐山市华辉金属制品有限公司</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>南通市崇川区帅昌贸易有限公司</t>
+          <t>嘉兴星驰包装材料有限公司</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -4208,7 +4196,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr"/>
@@ -4216,7 +4204,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>南通玖兴建设集团有限公司</t>
+          <t>嘉吉饲料（天津）有限公司</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -4226,7 +4214,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr"/>
@@ -4234,7 +4222,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>博白县那林镇多福养鸡专业合作社</t>
+          <t>嘉悦物产集团有限公司</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -4244,7 +4232,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr"/>
@@ -4252,7 +4240,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>吉林普康农业有限公司</t>
+          <t>四川省乐山市明仕农业发展有限公司</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -4270,83 +4258,95 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>周琎</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>国信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>呼伦贝尔上丰管道有限公司</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr"/>
+          <t>国投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨领骏商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr"/>
+          <t>国海良时期货有限公司</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>唐人神集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr"/>
+          <t>国联期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>唐山市华辉金属制品有限公司</t>
+          <t>夏邑县曹集乡华鑫养殖场</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr"/>
@@ -4364,25 +4364,29 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>嘉吉饲料（天津）有限公司</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr"/>
+          <t>大地期货有限公司</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>嘉悦物产集团有限公司</t>
+          <t>天津北宁科技有限公司</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -4392,7 +4396,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr"/>
@@ -4400,7 +4404,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>四川省乐山市明仕农业发展有限公司</t>
+          <t>宁夏新海恒基贸易有限公司</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -4410,7 +4414,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
@@ -4418,51 +4422,43 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>国信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>宁波市桐易广告影视传媒有限公司</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>国投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>宁波穗淼贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>国海良时期货有限公司</t>
+          <t>宁波静一私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -4472,41 +4468,37 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>国联期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>安徽骄阳电力科技有限公司</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>夏邑县曹集乡华鑫养殖场</t>
+          <t>安阳国匠环境科技有限公司</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -4516,7 +4508,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr"/>
@@ -4524,7 +4516,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>大地期货有限公司</t>
+          <t>宏源期货有限公司</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -4546,83 +4538,87 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>天津北宁科技有限公司</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>太仓景高汽车零部件有限公司</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司广东分公司</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>孟明</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>宜宾丝丽雅集团有限公司</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>宁波卓远健康管理咨询有限公司</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr"/>
+          <t>富宝账号维护</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>宁波海铨智能设备制造有限公司</t>
+          <t>富邦橡胶（浙江）有限公司</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -4640,7 +4636,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>宁波穗淼贸易有限公司</t>
+          <t>富邦资源控股集团有限公司</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -4658,29 +4654,25 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>宁波静一私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>山东卓创资讯股份有限公司</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>安庆市益农农业发展有限公司</t>
+          <t>山东嘉璐生物科技有限公司</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -4690,7 +4682,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr"/>
@@ -4698,7 +4690,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>安徽贾维斯家居有限公司</t>
+          <t>山东成武吉乐原禽业育种有限公司</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -4708,7 +4700,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr"/>
@@ -4716,47 +4708,47 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>安阳国匠环境科技有限公司</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr"/>
+          <t>山东港口投资控股有限公司</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>宏德私募基金管理（北京）有限公司</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>山东金工机电工业有限公司</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
+          <t>山东齐盛期货有限公司</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -4778,7 +4770,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
+          <t>山东齐盛期货有限公司福建分公司</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -4793,36 +4785,32 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司广东分公司</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>山西鑫辉食品股份有限公司</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>宜宾丝丽雅集团有限公司</t>
+          <t>峨眉山市民生源生态农业科技发展有限公司</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -4832,7 +4820,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr"/>
@@ -4840,7 +4828,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>富邦橡胶（浙江）有限公司</t>
+          <t>常州奕允供应链管理有限公司</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -4850,7 +4838,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr"/>
@@ -4858,7 +4846,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>富邦资源控股集团有限公司</t>
+          <t>广东五湖农业科技有限公司</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -4868,7 +4856,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr"/>
@@ -4876,7 +4864,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>山东一民私募基金管理有限公司</t>
+          <t>广东厚方投资管理有限公司</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -4898,7 +4886,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>山东丰元锂能科技有限公司</t>
+          <t>广东嘉誉化工有限公司</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -4916,25 +4904,29 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>山东卓创资讯股份有限公司</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D213" s="4" t="inlineStr"/>
+          <t>广东横琴均成私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>山东嘉璐生物科技有限公司</t>
+          <t>广州市佰胜展览服务有限公司</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -4944,7 +4936,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr"/>
@@ -4952,7 +4944,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>山东成武吉乐原禽业育种有限公司</t>
+          <t>广州市嘉玉华粮油贸易有限公司</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -4962,7 +4954,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr"/>
@@ -4970,51 +4962,43 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>山东港口投资控股有限公司</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
+          <t>广州市天塑塑料制品有限公司</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>山东融升私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广州正鲜农牧科技有限公司</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>山东鸿烨铭阳投资有限公司</t>
+          <t>广州汇川私募证券投资基金管理有限公司</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -5036,51 +5020,43 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C219" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>广州泰禾能源有限公司</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>广东厚方投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广州越秀企业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>广东嘉誉化工有限公司</t>
+          <t>广西聚则新贸易有限公司</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -5090,7 +5066,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr"/>
@@ -5098,7 +5074,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>广东横琴均成私募基金管理有限公司</t>
+          <t>建信期货有限责任公司</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -5108,19 +5084,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>广东盈峰发展有限公司</t>
+          <t>徐州好益佳食品有限公司</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -5130,7 +5106,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -5138,25 +5114,29 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>广州丰翊能源有限公司</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="inlineStr"/>
+          <t>徽商期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>广州市佰胜展览服务有限公司</t>
+          <t>惠州市小象智能科技有限公司</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -5174,7 +5154,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>广州市嘉玉华粮油贸易有限公司</t>
+          <t>成都世纪昊天商贸有限公司</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -5192,7 +5172,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区昊赢服装商行</t>
+          <t>成都岭南春商贸有限公司</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -5210,7 +5190,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>广州汇川私募证券投资基金管理有限公司</t>
+          <t>招商期货有限公司</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -5220,55 +5200,63 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>广州泰禾能源有限公司</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr"/>
+          <t>敦和资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>广州越秀企业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr"/>
+          <t>新湖期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>建信期货有限责任公司</t>
+          <t>方正中期期货有限公司</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -5290,7 +5278,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司上海分公司</t>
+          <t>方正证券股份有限公司</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -5305,36 +5293,32 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>证券公司分公司</t>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>徽商期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>日照泰高亚昊饲料科技有限公司</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>惠州市小象智能科技有限公司</t>
+          <t>昆山民巨电子科技有限公司</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -5344,7 +5328,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr"/>
@@ -5352,7 +5336,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>成都岭南春商贸有限公司</t>
+          <t>昆山玉高精密设备有限公司</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -5362,7 +5346,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr"/>
@@ -5370,7 +5354,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>招商期货有限公司</t>
+          <t>易持（厦门）私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -5380,41 +5364,41 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>敦和资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>李平野</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>新湖期货股份有限公司</t>
+          <t>杭州孚盈投资管理有限公司</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -5424,19 +5408,19 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>方正中期期货有限公司</t>
+          <t>杭州山量投资管理有限公司</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -5446,41 +5430,37 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>方正证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>杭州朝霞实业有限公司</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>无锡茂丰建设工程有限公司</t>
+          <t>杭州纳永实业有限公司</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -5490,7 +5470,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr"/>
@@ -5498,25 +5478,29 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>昆山玉高精密设备有限公司</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr"/>
+          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>易持（厦门）私募基金管理有限公司</t>
+          <t>格林大华期货有限公司</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -5526,81 +5510,81 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>昶德（山东）国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr"/>
+          <t>正信期货有限公司</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>李平野</t>
-        </is>
-      </c>
-      <c r="B245" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C245" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D245" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>武汉市钧凌实业投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>杨振东</t>
-        </is>
-      </c>
-      <c r="B246" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C246" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>武汉数商科技有限公司</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>杭州三毛商业控股有限公司</t>
+          <t>武汉苍鹰贸易有限公司</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -5610,7 +5594,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr"/>
@@ -5618,7 +5602,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>杭州孚盈投资管理有限公司</t>
+          <t>永安期货股份有限公司</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -5628,103 +5612,95 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>杭州孚盈投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C249" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>永富物产有限公司</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>杭州山量投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>永康市浩资建筑材料厂</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>杭州朝霞实业有限公司</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr"/>
+          <t>汇丰前海证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>外资券商</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>杭州碳硅私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C252" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>汕头市诚兴塑化有限公司</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>杭州纳永实业有限公司</t>
+          <t>江山市永丰化建有限公司</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -5742,69 +5718,65 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>杭州通宇实业有限公司</t>
-        </is>
-      </c>
-      <c r="B254" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D254" s="4" t="inlineStr"/>
+          <t>江海汇鑫期货有限公司</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>格林大华期货有限公司</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C255" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>江西国元农业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>正信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>河北卓峰化肥有限公司</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>正大康地（开封）生物科技有限公司</t>
+          <t>河北古月坊农业科技有限公司</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -5822,29 +5794,25 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>武汉市钧凌实业投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>河南君友商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>武汉苍鹰贸易有限公司</t>
+          <t>河南省才聚万锦生猪贸易有限公司</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -5854,7 +5822,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr"/>
@@ -5862,51 +5830,43 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>民生证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>河南金之晟养殖有限公司</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>永安期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D261" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>河南鑫诺农业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>永富物产有限公司</t>
+          <t>泉州市润心塑胶科技有限公司</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -5916,7 +5876,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr"/>
@@ -5924,7 +5884,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>永康市浩资建筑材料厂</t>
+          <t>泰安市泰山区海阔饲料销售中心</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -5934,7 +5894,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr"/>
@@ -5942,43 +5902,51 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>汕头市诚兴塑化有限公司</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D264" s="4" t="inlineStr"/>
+          <t>浙商期货有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>江山市永丰化建有限公司</t>
-        </is>
-      </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D265" s="4" t="inlineStr"/>
+          <t>浙江南华资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>江海汇鑫期货有限公司</t>
+          <t>浙江新世纪期货有限公司</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -6000,7 +5968,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>江苏创一精锻有限公司</t>
+          <t>浙江旺璐物资有限公司</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -6010,7 +5978,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr"/>
@@ -6018,7 +5986,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>江西国元农业发展集团有限公司</t>
+          <t>浙江杭实善成实业有限公司</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -6028,7 +5996,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr"/>
@@ -6036,43 +6004,51 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>沈阳市克达饲料有限公司</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D269" s="4" t="inlineStr"/>
+          <t>浙江金榕树投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>河北允硕供应链有限责任公司</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D270" s="4" t="inlineStr"/>
+          <t>海南佳岳私募证券基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>河北卓峰化肥有限公司</t>
+          <t>海南农垦草畜猪业有限公司</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -6082,7 +6058,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr"/>
@@ -6090,7 +6066,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>河南八亿能源供应链有限公司</t>
+          <t>海宁帕提时尚服饰有限公司</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -6100,7 +6076,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr"/>
@@ -6108,25 +6084,29 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>河南合鑫房地产开发有限公司</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D273" s="4" t="inlineStr"/>
+          <t>海通期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>河南恒益供应链管理有限公司</t>
+          <t>淄博市多盈数据智能有限公司</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -6144,7 +6124,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>河南省才聚万锦生猪贸易有限公司</t>
+          <t>深圳市兵法技术有限公司</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -6154,7 +6134,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr"/>
@@ -6162,7 +6142,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>河南金之晟养殖有限公司</t>
+          <t>深圳市慧网第三方信息咨询有限公司</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -6172,7 +6152,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr"/>
@@ -6180,7 +6160,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>河南鑫诺农业发展有限公司</t>
+          <t>深圳市汇淼淼贸易有限公司</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -6190,7 +6170,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr"/>
@@ -6198,7 +6178,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>泉州市润心塑胶科技有限公司</t>
+          <t>深圳市真利视界科技有限公司</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -6208,7 +6188,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr"/>
@@ -6216,7 +6196,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>浙商期货有限公司上海分公司</t>
+          <t>深圳市鼎泉盛世投资管理有限公司</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -6226,19 +6206,19 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>期货公司分公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>浙江南华资本管理有限公司</t>
+          <t>混沌天成期货股份有限公司上海分公司</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -6248,41 +6228,37 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>券商私募（另类投资）</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>浙江新世纪期货有限公司</t>
-        </is>
-      </c>
-      <c r="B281" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C281" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D281" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>湖南中升物贸有限责任公司</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>浙江杭实善成实业有限公司</t>
+          <t>潍坊方程式生物化工有限公司</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -6292,7 +6268,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr"/>
@@ -6300,7 +6276,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>浙江涌汪船务工程有限公司</t>
+          <t>烟台东诚果业有限公司</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -6310,7 +6286,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr"/>
@@ -6318,29 +6294,25 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>浙江金榕树投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C284" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D284" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>牧原食品集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>海南佳岳私募证券基金管理有限公司</t>
+          <t>物产中大期货有限公司</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -6350,113 +6322,121 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>海南汇新达供应链管理有限公司</t>
-        </is>
-      </c>
-      <c r="B286" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D286" s="4" t="inlineStr"/>
+          <t>王斌华</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>海牛金属资源（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D287" s="4" t="inlineStr"/>
+          <t>王绎翔</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>淄博市多盈数据智能有限公司</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C288" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D288" s="4" t="inlineStr"/>
+          <t>百万期货</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D288" s="6" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>深圳升程投资控股有限公司</t>
-        </is>
-      </c>
-      <c r="B289" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C289" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D289" s="3" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
+          <t>石景涛</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>深圳市卓尔创科技有限公司</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C290" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D290" s="4" t="inlineStr"/>
+          <t>红期分享测试</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D290" s="6" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>深圳市自在天地科技有限公司</t>
+          <t>绵阳市乐事多食品有限公司</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -6466,7 +6446,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr"/>
@@ -6474,25 +6454,29 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>深圳市鸿宇食品有限公司</t>
-        </is>
-      </c>
-      <c r="B292" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C292" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D292" s="4" t="inlineStr"/>
+          <t>胡洋洋</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>深圳新康娱科技有限公司</t>
+          <t>芜湖中铸材料科技有限公司</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -6502,7 +6486,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr"/>
@@ -6510,7 +6494,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>深圳诺普信作物科学股份有限公司</t>
+          <t>苏州万家鲜食品有限公司</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -6528,7 +6512,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>混沌天成期货股份有限公司上海分公司</t>
+          <t>苏州创元和赢资本管理有限公司</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -6538,55 +6522,63 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>期货公司分公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>清华大学量化投资</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr"/>
+          <t>苏州创元投资发展（集团）有限公司</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>温州市温纳汽车配件有限公司</t>
-        </is>
-      </c>
-      <c r="B297" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C297" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D297" s="4" t="inlineStr"/>
+          <t>苏豪弘业期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>湖南中升物贸有限责任公司</t>
+          <t>蔚县怡洲商贸有限公司</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -6604,47 +6596,47 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>潍坊方程式生物化工有限公司</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D299" s="4" t="inlineStr"/>
+          <t>融创智富（深圳）资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>物产中大期货有限公司</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C300" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D300" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>衡水宝泰机械配件制造有限公司</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>物产中大欧泰有限公司</t>
+          <t>许昌市同庆纺织实业有限公司</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -6654,7 +6646,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr"/>
@@ -6662,65 +6654,65 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>珠海新文华纸业有限公司</t>
-        </is>
-      </c>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C302" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D302" s="4" t="inlineStr"/>
+          <t>诸城市大科建材营销店（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>百万期货</t>
-        </is>
-      </c>
-      <c r="B303" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C303" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D303" s="6" t="inlineStr"/>
+          <t>谷实生物科技（天津）有限公司</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>石景涛</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>账号已注销</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C304" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D304" s="6" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>福州市晋安区王庄季城河电子产品商行</t>
+          <t>贵州百农汇农业集团有限公司</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -6730,7 +6722,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr"/>
@@ -6738,65 +6730,65 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>福建省昌晶恒业化工有限公司</t>
-        </is>
-      </c>
-      <c r="B306" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C306" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D306" s="4" t="inlineStr"/>
+          <t>贵阳新泰投资有限公司</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>福能期货股份有限公司莆田营业部</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C307" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D307" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>赣州盈实信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>红期分享测试</t>
-        </is>
-      </c>
-      <c r="B308" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C308" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D308" s="6" t="inlineStr"/>
+          <t>路源（大连）石化产品有限公司</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>绵阳市乐事多食品有限公司</t>
+          <t>邢台麦之多商贸有限公司</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -6806,7 +6798,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr"/>
@@ -6814,47 +6806,47 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>肇庆市国勇农林发展有限公司</t>
-        </is>
-      </c>
-      <c r="B310" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C310" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D310" s="4" t="inlineStr"/>
+          <t>郁卫华</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>胡洋洋</t>
-        </is>
-      </c>
-      <c r="B311" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C311" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D311" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>郑州市赛迪商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>苏州万家鲜食品有限公司</t>
+          <t>重庆日邦商贸有限公司</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -6864,7 +6856,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr"/>
@@ -6872,51 +6864,43 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>苏州创元和赢资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C313" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D313" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>重庆泰戈新能源发展有限公司</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>苏州创元投资发展（集团）有限公司</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D314" s="3" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
+          <t>重庆航铝物资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>苏豪弘业期货股份有限公司</t>
+          <t>银河期货有限公司</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -6938,43 +6922,51 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>蔚县怡洲商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B316" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C316" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D316" s="4" t="inlineStr"/>
+          <t>长安期货有限公司</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>衡水宝泰机械配件制造有限公司</t>
-        </is>
-      </c>
-      <c r="B317" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C317" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D317" s="4" t="inlineStr"/>
+          <t>长江期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>西安风启网络科技有限公司</t>
+          <t>长沙市玉阅咨询服务有限公司</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -6992,7 +6984,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>谷实生物科技（天津）有限公司</t>
+          <t>阿克苏市恒鑫顺调料批发部</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -7002,7 +6994,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr"/>
@@ -7010,25 +7002,29 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>路源（大连）石化产品有限公司</t>
-        </is>
-      </c>
-      <c r="B320" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C320" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D320" s="4" t="inlineStr"/>
+          <t>陈荣跃</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>辽宁荷花国际旅行社有限公司</t>
+          <t>陕西亿佳农牧科技有限公司</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -7038,7 +7034,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr"/>
@@ -7046,7 +7042,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>邹平森格铝材有限公司</t>
+          <t>隆昌博文视光眼镜有限责任公司</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -7056,7 +7052,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr"/>
@@ -7064,29 +7060,25 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>郁卫华</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>青岛信达新材料有限公司</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>郑州市赛迪商贸有限公司</t>
+          <t>青岛柏霖农业科技发展有限公司</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -7096,7 +7088,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr"/>
@@ -7104,7 +7096,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>郑州诚磐贸易有限公司</t>
+          <t>青岛金月亮建设工程有限公司</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -7114,7 +7106,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr"/>
@@ -7122,29 +7114,25 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>郭美成</t>
-        </is>
-      </c>
-      <c r="B326" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C326" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D326" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>黄梅县泰源棉业有限公司</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>重庆亿赐元企业管理咨询有限公司</t>
+          <t>黑山县贺兴养殖专业合作社</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -7154,7 +7142,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr"/>
@@ -7162,25 +7150,29 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>重庆日邦商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B328" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C328" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D328" s="4" t="inlineStr"/>
+          <t>黑龙江优上家族投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>重庆臻道行文化传播有限公司</t>
+          <t>鼎成纺织（南通）有限公司</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
@@ -7190,307 +7182,13 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr"/>
     </row>
-    <row r="330">
-      <c r="A330" s="2" t="inlineStr">
-        <is>
-          <t>金华新益家企业管理咨询有限公司</t>
-        </is>
-      </c>
-      <c r="B330" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C330" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D330" s="4" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>银河期货有限公司</t>
-        </is>
-      </c>
-      <c r="B331" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C331" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D331" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>银河期货有限公司</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C332" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D332" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="inlineStr">
-        <is>
-          <t>销售事业部</t>
-        </is>
-      </c>
-      <c r="B333" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C333" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D333" s="6" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>锦泰期货有限公司常熟营业部</t>
-        </is>
-      </c>
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C334" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D334" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>长安期货有限公司</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C335" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>长江期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D336" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>长沙市玉阅咨询服务有限公司</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>陕西亿佳农牧科技有限公司</t>
-        </is>
-      </c>
-      <c r="B338" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C338" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D338" s="4" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>陕西泓名佳润能源科技有限公司</t>
-        </is>
-      </c>
-      <c r="B339" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C339" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D339" s="4" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>隆昌博文视光眼镜有限责任公司</t>
-        </is>
-      </c>
-      <c r="B340" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D340" s="4" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>青岛中天信国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B341" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D341" s="4" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>青岛金晟新能源有限公司</t>
-        </is>
-      </c>
-      <c r="B342" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D342" s="4" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>黑山县贺兴养殖专业合作社</t>
-        </is>
-      </c>
-      <c r="B343" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C343" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D343" s="4" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="inlineStr">
-        <is>
-          <t>黑龙江优上家族投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B344" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C344" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D344" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D344"/>
+  <autoFilter ref="A1:D329"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7523,7 +7221,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -7533,7 +7231,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
@@ -7543,7 +7241,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -7563,7 +7261,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/客户分类结果.xlsx
+++ b/客户分类结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$373</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D329"/>
+  <dimension ref="A1:D373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海众壹资产管理有限公司</t>
+          <t>上海亿衍私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -642,64 +642,60 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海八桂资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海冕泓实业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海冕泓实业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+          <t>上海双隆投资有限公司</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海双隆投资有限公司</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海均元址元文化传媒有限责任公司</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海河清龙樾企业管理有限公司</t>
+          <t>上海港耀科技有限公司</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -744,7 +740,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海港耀科技有限公司</t>
+          <t>上海炫健体育文化传播有限公司</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -762,7 +758,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海申袆实业有限公司</t>
+          <t>上海然盛贸易有限公司</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -820,29 +816,25 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海维万私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海翔涌化工国际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海翔涌化工国际贸易有限公司</t>
+          <t>上海融合良谷供应链有限公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -852,7 +844,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -944,38 +936,46 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>东方龙木（海南）国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>东莞市大岭山赣进粮油经营部</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -2190,7 +2190,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>个体期货</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -3202,367 +3202,403 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>中信建投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>中信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>中原期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>中国平安保险（集团）股份有限公司</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>保险集团</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>中基宁波集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>中央储备粮辽东湾直属库有限公司</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>中泰期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>中粮农业产业管理服务有限公司</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>中粮期货有限公司</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>中衍期货有限公司</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>中间市场部</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>临清市翔茂木材加工厂</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>云南程鹏饲料有限责任公司</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>五矿期货有限公司</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>产品管理部</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>元氏县炜淼农业开发有限公司</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>光大期货有限公司</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>全国畜牧总站</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr"/>
+          <t>个体期货</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>兴业期货有限公司</t>
+          <t>中信建投期货有限公司</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -3584,7 +3620,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
+          <t>中信期货有限公司</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -3594,19 +3630,19 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>证券公司</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>兴证期货有限公司</t>
+          <t>中原期货股份有限公司</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -3628,7 +3664,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>冀交港口物流唐山有限公司</t>
+          <t>中国供销集团延长果业有限责任公司</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -3638,7 +3674,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3646,47 +3682,47 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>冠县乐园养殖有限公司</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>中国平安保险（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>刘晓明</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中基宁波集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>北京六合粮源农业科技有限公司</t>
+          <t>中央储备粮辽东湾直属库有限公司</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -3704,7 +3740,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>北京国康未来医学研究院</t>
+          <t>中山麦卡迪数码科技有限公司</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -3722,123 +3758,127 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>北京摩卡站餐饮管理有限公司</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
+          <t>中泰期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>北京星鹏联海私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>中粮农业产业管理服务有限公司</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>北京永盛芳科贸有限公司</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr"/>
+          <t>中粮期货有限公司</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>北京盛维弘波管理顾问有限公司</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>中衍期货有限公司</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>北京顶峰时刻科技有限公司</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr"/>
+          <t>中间市场部</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>华安期货有限责任公司青岛营业部</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>云南程鹏饲料有限责任公司</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司</t>
+          <t>五矿期货有限公司</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -3860,29 +3900,25 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司上海世纪大道营业部</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>产品管理部</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>华裕农业科技有限公司</t>
+          <t>元氏县炜淼农业开发有限公司</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -3900,7 +3936,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>华闻期货有限公司</t>
+          <t>光大期货有限公司</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -3922,65 +3958,69 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>南京洲利盛科技有限公司</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr"/>
+          <t>全国畜牧总站</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>南宁市荣泽钢材有限公司</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr"/>
+          <t>兴业期货有限公司</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>南志云</t>
-        </is>
-      </c>
-      <c r="B164" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D164" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>南通中睿投资有限公司</t>
+          <t>兴证期货有限公司</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -3990,19 +4030,19 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>南通市崇川区帅昌贸易有限公司</t>
+          <t>冀交港口物流唐山有限公司</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -4012,7 +4052,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
@@ -4020,7 +4060,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>南通鸿华化工有限公司</t>
+          <t>冠县乐园养殖有限公司</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -4030,7 +4070,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr"/>
@@ -4038,25 +4078,29 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>博白县那林镇多福养鸡专业合作社</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr"/>
+          <t>刘晓明</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>合肥神之手贸易有限公司</t>
+          <t>北京六合粮源农业科技有限公司</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -4066,7 +4110,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr"/>
@@ -4074,47 +4118,51 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>吉林普康农业有限公司</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr"/>
+          <t>北京厚奕投资有限公司</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>周琎</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>北京君和九思私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>呼伦贝尔上丰管道有限公司</t>
+          <t>北京国康未来医学研究院</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -4124,7 +4172,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr"/>
@@ -4132,7 +4180,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨领骏商贸有限公司</t>
+          <t>北京摩卡站餐饮管理有限公司</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -4142,7 +4190,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr"/>
@@ -4150,43 +4198,51 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>唐人神集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr"/>
+          <t>北京星鹏联海私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>唐山市华辉金属制品有限公司</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr"/>
+          <t>北京琮碧秋实私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>嘉兴星驰包装材料有限公司</t>
+          <t>北京盛维弘波管理顾问有限公司</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -4196,7 +4252,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr"/>
@@ -4204,149 +4260,149 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>嘉吉饲料（天津）有限公司</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr"/>
+          <t>华安期货有限责任公司青岛营业部</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>嘉悦物产集团有限公司</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
+          <t>华泰期货有限公司</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>四川省乐山市明仕农业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr"/>
+          <t>华泰期货有限公司上海世纪大道营业部</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>国信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>华裕农业科技有限公司</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>国投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>南京洲利盛科技有限公司</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>国海良时期货有限公司</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>南宁市荣泽钢材有限公司</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>国联期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>南志云</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>夏邑县曹集乡华鑫养殖场</t>
+          <t>南昌南鲸广告有限公司</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -4356,7 +4412,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr"/>
@@ -4364,7 +4420,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>大地期货有限公司</t>
+          <t>南通中睿投资有限公司</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -4374,19 +4430,19 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>天津北宁科技有限公司</t>
+          <t>南通市崇川区帅昌贸易有限公司</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -4396,7 +4452,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr"/>
@@ -4404,7 +4460,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>宁夏新海恒基贸易有限公司</t>
+          <t>南通鸿华化工有限公司</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -4414,7 +4470,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
@@ -4422,7 +4478,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>宁波市桐易广告影视传媒有限公司</t>
+          <t>博白县那林镇多福养鸡专业合作社</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -4432,7 +4488,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr"/>
@@ -4440,7 +4496,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>宁波穗淼贸易有限公司</t>
+          <t>合肥神之手贸易有限公司</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -4458,29 +4514,25 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>宁波静一私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>吉林普康农业有限公司</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>安徽骄阳电力科技有限公司</t>
+          <t>哈尔滨领骏商贸有限公司</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -4490,7 +4542,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr"/>
@@ -4498,7 +4550,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>安阳国匠环境科技有限公司</t>
+          <t>唐人神集团股份有限公司</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -4508,7 +4560,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr"/>
@@ -4516,73 +4568,61 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>唐山市华辉金属制品有限公司</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>嘉兴星驰包装材料有限公司</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司广东分公司</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>嘉吉饲料（天津）有限公司</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>宜宾丝丽雅集团有限公司</t>
+          <t>嘉悦物产集团有限公司</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -4592,7 +4632,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr"/>
@@ -4600,25 +4640,25 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>富宝账号维护</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D197" s="6" t="inlineStr"/>
+          <t>四川安卓联商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>富邦橡胶（浙江）有限公司</t>
+          <t>四川成都彭州三电电缆制造有限公司</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -4636,7 +4676,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>富邦资源控股集团有限公司</t>
+          <t>四川省乐山市明仕农业发展有限公司</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -4646,7 +4686,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr"/>
@@ -4654,25 +4694,29 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>山东卓创资讯股份有限公司</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr"/>
+          <t>国信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>山东嘉璐生物科技有限公司</t>
+          <t>国华工程科技（集团）有限责任公司</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -4682,7 +4726,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr"/>
@@ -4690,25 +4734,29 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>山东成武吉乐原禽业育种有限公司</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="inlineStr"/>
+          <t>国投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>山东港口投资控股有限公司</t>
+          <t>国泰君安期货有限公司深圳福田分公司</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -4718,37 +4766,41 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>私募投资集团</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>山东金工机电工业有限公司</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr"/>
+          <t>国海良时期货有限公司</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司</t>
+          <t>国联期货股份有限公司</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -4770,29 +4822,25 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司福建分公司</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>塞洪（上海）贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>山西鑫辉食品股份有限公司</t>
+          <t>夏邑县曹集乡华鑫养殖场</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -4802,7 +4850,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr"/>
@@ -4810,43 +4858,51 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>峨眉山市民生源生态农业科技发展有限公司</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr"/>
+          <t>大地期货有限公司</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>常州奕允供应链管理有限公司</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr"/>
+          <t>大地期货有限公司温州分公司</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>广东五湖农业科技有限公司</t>
+          <t>大连德佰电子商务有限公司</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -4856,7 +4912,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr"/>
@@ -4864,69 +4920,65 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>广东厚方投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>天津北宁科技有限公司</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>广东嘉誉化工有限公司</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D212" s="4" t="inlineStr"/>
+          <t>天津奇略云天科技合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>广东横琴均成私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>宁波市桐易广告影视传媒有限公司</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>广州市佰胜展览服务有限公司</t>
+          <t>宁波穗淼贸易有限公司</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -4936,7 +4988,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr"/>
@@ -4944,25 +4996,29 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>广州市嘉玉华粮油贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="inlineStr"/>
+          <t>宁波静一私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>广州市天塑塑料制品有限公司</t>
+          <t>安徽和协园艺有限公司</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -4972,7 +5028,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr"/>
@@ -4980,7 +5036,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>广州正鲜农牧科技有限公司</t>
+          <t>安徽省安庆市科大包装材料有限公司</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -4990,7 +5046,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr"/>
@@ -4998,29 +5054,25 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>广州汇川私募证券投资基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>安徽骄阳电力科技有限公司</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>广州泰禾能源有限公司</t>
+          <t>安阳国匠环境科技有限公司</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -5030,7 +5082,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr"/>
@@ -5038,65 +5090,69 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>广州越秀企业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>广西聚则新贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司广东分公司</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>建信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>宜宾丝丽雅集团有限公司</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>徐州好益佳食品有限公司</t>
+          <t>宿州市隆润农牧有限公司</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -5106,7 +5162,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -5114,29 +5170,25 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>徽商期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>富宝账号维护</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>惠州市小象智能科技有限公司</t>
+          <t>富邦资源控股集团有限公司</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -5146,7 +5198,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr"/>
@@ -5154,7 +5206,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>成都世纪昊天商贸有限公司</t>
+          <t>山东嘉璐生物科技有限公司</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -5164,7 +5216,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr"/>
@@ -5172,7 +5224,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>成都岭南春商贸有限公司</t>
+          <t>山东成武吉乐原禽业育种有限公司</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -5182,7 +5234,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr"/>
@@ -5190,73 +5242,61 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>招商期货有限公司</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东智义恒商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>敦和资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>山东祖豪物流有限公司</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>新湖期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东金工机电工业有限公司</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>方正中期期货有限公司</t>
+          <t>山东齐盛期货有限公司</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -5278,7 +5318,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>方正证券股份有限公司</t>
+          <t>山东齐盛期货有限公司福建分公司</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -5288,19 +5328,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>证券公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>日照泰高亚昊饲料科技有限公司</t>
+          <t>山西鑫辉食品股份有限公司</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -5310,7 +5350,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr"/>
@@ -5318,7 +5358,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>昆山民巨电子科技有限公司</t>
+          <t>常州铭梵环境咨询有限公司</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -5328,7 +5368,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr"/>
@@ -5336,7 +5376,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>昆山玉高精密设备有限公司</t>
+          <t>广东五湖农业科技有限公司</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -5346,7 +5386,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr"/>
@@ -5354,7 +5394,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>易持（厦门）私募基金管理有限公司</t>
+          <t>广东厚方投资管理有限公司</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -5376,29 +5416,25 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>李平野</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>广东嘉誉化工有限公司</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>杭州孚盈投资管理有限公司</t>
+          <t>广东横琴均成私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -5420,29 +5456,25 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>杭州山量投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C239" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广州华创山海贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>杭州朝霞实业有限公司</t>
+          <t>广州市嘉玉华粮油贸易有限公司</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -5452,7 +5484,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr"/>
@@ -5460,7 +5492,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>杭州纳永实业有限公司</t>
+          <t>广州市天塑塑料制品有限公司</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -5470,7 +5502,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr"/>
@@ -5478,29 +5510,25 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>广州正鲜农牧科技有限公司</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>格林大华期货有限公司</t>
+          <t>广州汇川私募证券投资基金管理有限公司</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -5510,81 +5538,77 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>正信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>广州越秀企业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>武汉市钧凌实业投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C245" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广西聚则新贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>武汉数商科技有限公司</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr"/>
+          <t>建信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>武汉苍鹰贸易有限公司</t>
+          <t>张家港市星恒工具有限公司</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -5594,7 +5618,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr"/>
@@ -5602,47 +5626,47 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>永安期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>徐州好益佳食品有限公司</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>永富物产有限公司</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D249" s="4" t="inlineStr"/>
+          <t>徽商期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>永康市浩资建筑材料厂</t>
+          <t>惠州市小象智能科技有限公司</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -5652,7 +5676,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr"/>
@@ -5660,29 +5684,25 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>汇丰前海证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>外资券商</t>
-        </is>
-      </c>
+          <t>成都世纪昊天商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>汕头市诚兴塑化有限公司</t>
+          <t>成都岭南春商贸有限公司</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -5700,25 +5720,29 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>江山市永丰化建有限公司</t>
-        </is>
-      </c>
-      <c r="B253" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="inlineStr"/>
+          <t>房兴旭</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>江海汇鑫期货有限公司</t>
+          <t>招商期货有限公司</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -5740,7 +5764,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>江西国元农业发展集团有限公司</t>
+          <t>新享数成（济南）数字科技有限公司</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -5750,7 +5774,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr"/>
@@ -5758,25 +5782,29 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>河北卓峰化肥有限公司</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr"/>
+          <t>新湖期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>河北古月坊农业科技有限公司</t>
+          <t>新疆融创汇欣物产农业有限责任公司</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -5786,7 +5814,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr"/>
@@ -5794,43 +5822,51 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>河南君友商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr"/>
+          <t>方正中期期货有限公司</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>河南省才聚万锦生猪贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr"/>
+          <t>方正证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>河南金之晟养殖有限公司</t>
+          <t>日照泰高亚昊饲料科技有限公司</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -5848,7 +5884,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>河南鑫诺农业发展有限公司</t>
+          <t>昆山民巨电子科技有限公司</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -5858,7 +5894,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr"/>
@@ -5866,25 +5902,29 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>泉州市润心塑胶科技有限公司</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D262" s="4" t="inlineStr"/>
+          <t>易持（厦门）私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>泰安市泰山区海阔饲料销售中心</t>
+          <t>曹县砖庙镇凯悦养殖场</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -5902,51 +5942,47 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>浙商期货有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D264" s="6" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>浙江南华资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>券商私募（另类投资）</t>
+          <t>李平野</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>浙江新世纪期货有限公司</t>
+          <t>杭州孚盈投资管理有限公司</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -5956,37 +5992,41 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>浙江旺璐物资有限公司</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D267" s="4" t="inlineStr"/>
+          <t>杭州山量投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>浙江杭实善成实业有限公司</t>
+          <t>杭州朝霞实业有限公司</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -5996,7 +6036,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr"/>
@@ -6004,87 +6044,87 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>浙江金榕树投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>杭州纳永实业有限公司</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>海南佳岳私募证券基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>杭州花生壳科技有限公司</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>海南农垦草畜猪业有限公司</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D271" s="4" t="inlineStr"/>
+          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>海宁帕提时尚服饰有限公司</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D272" s="4" t="inlineStr"/>
+          <t>格林大华期货有限公司</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>海通期货股份有限公司</t>
+          <t>正信期货有限公司</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -6106,25 +6146,29 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>淄博市多盈数据智能有限公司</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr"/>
+          <t>武汉市钧凌实业投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>深圳市兵法技术有限公司</t>
+          <t>武汉数商科技有限公司</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -6142,7 +6186,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>深圳市慧网第三方信息咨询有限公司</t>
+          <t>武汉苍鹰贸易有限公司</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -6152,7 +6196,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr"/>
@@ -6160,25 +6204,29 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>深圳市汇淼淼贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D277" s="4" t="inlineStr"/>
+          <t>永安期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>深圳市真利视界科技有限公司</t>
+          <t>永康市浩资建筑材料厂</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -6188,7 +6236,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr"/>
@@ -6196,7 +6244,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>深圳市鼎泉盛世投资管理有限公司</t>
+          <t>汇丰前海证券有限责任公司</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -6206,41 +6254,37 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>外资券商</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>混沌天成期货股份有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C280" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>汕头市诚兴塑化有限公司</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>湖南中升物贸有限责任公司</t>
+          <t>江山市永丰化建有限公司</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -6258,25 +6302,29 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>潍坊方程式生物化工有限公司</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D282" s="4" t="inlineStr"/>
+          <t>江海汇鑫期货有限公司</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>烟台东诚果业有限公司</t>
+          <t>江西中啟建设工程有限公司</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -6286,7 +6334,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr"/>
@@ -6294,7 +6342,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>牧原食品集团股份有限公司</t>
+          <t>江西国元农业发展集团有限公司</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -6312,131 +6360,115 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>物产中大期货有限公司</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C285" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D285" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>江西状元郎食品集团有限公司</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>王斌华</t>
-        </is>
-      </c>
-      <c r="B286" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C286" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D286" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河北卓峰化肥有限公司</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>王绎翔</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C287" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D287" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河北古月坊农业科技有限公司</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>百万期货</t>
-        </is>
-      </c>
-      <c r="B288" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C288" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D288" s="6" t="inlineStr"/>
+          <t>河南君友商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>石景涛</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C289" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河南省冠林贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>红期分享测试</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C290" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D290" s="6" t="inlineStr"/>
+          <t>河南省才聚万锦生猪贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>绵阳市乐事多食品有限公司</t>
+          <t>河南金之晟养殖有限公司</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -6446,7 +6478,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr"/>
@@ -6454,29 +6486,25 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>胡洋洋</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C292" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河南鑫诺农业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>芜湖中铸材料科技有限公司</t>
+          <t>泉州市润心塑胶科技有限公司</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -6494,7 +6522,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>苏州万家鲜食品有限公司</t>
+          <t>泰安市泰山区海阔饲料销售中心</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -6504,7 +6532,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr"/>
@@ -6512,51 +6540,43 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>苏州创元和赢资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D295" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>济宁市明辰木业有限公司</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>苏州创元投资发展（集团）有限公司</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C296" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D296" s="3" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
+          <t>浙商中拓集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>苏豪弘业期货股份有限公司</t>
+          <t>浙商期货有限公司上海分公司</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -6571,14 +6591,14 @@
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>蔚县怡洲商贸有限公司</t>
+          <t>浙江华道律师事务所</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -6588,7 +6608,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr"/>
@@ -6596,47 +6616,47 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>融创智富（深圳）资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C299" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D299" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>浙江卓诗尼鞋业有限公司</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>衡水宝泰机械配件制造有限公司</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D300" s="4" t="inlineStr"/>
+          <t>浙江南华资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>许昌市同庆纺织实业有限公司</t>
+          <t>浙江响农农副产品有限公司</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -6646,7 +6666,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr"/>
@@ -6654,29 +6674,29 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>诸城市大科建材营销店（个体工商户）</t>
-        </is>
-      </c>
-      <c r="B302" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C302" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D302" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>浙江新世纪期货有限公司</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>谷实生物科技（天津）有限公司</t>
+          <t>浙江旺璐物资有限公司</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -6686,7 +6706,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr"/>
@@ -6694,65 +6714,65 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>账号已注销</t>
-        </is>
-      </c>
-      <c r="B304" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C304" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D304" s="6" t="inlineStr"/>
+          <t>浙江杭实善成实业有限公司</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>贵州百农汇农业集团有限公司</t>
-        </is>
-      </c>
-      <c r="B305" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D305" s="4" t="inlineStr"/>
+          <t>海南佳岳私募证券基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>贵阳新泰投资有限公司</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C306" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D306" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>海南农垦草畜猪业有限公司</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>赣州盈实信息科技有限公司</t>
+          <t>海宁帕提时尚服饰有限公司</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -6762,7 +6782,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr"/>
@@ -6770,25 +6790,29 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>路源（大连）石化产品有限公司</t>
-        </is>
-      </c>
-      <c r="B308" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C308" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="inlineStr"/>
+          <t>海通期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>邢台麦之多商贸有限公司</t>
+          <t>淄博市多盈数据智能有限公司</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -6798,7 +6822,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr"/>
@@ -6806,29 +6830,29 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>郁卫华</t>
-        </is>
-      </c>
-      <c r="B310" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C310" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D310" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>深圳中盈蓝景私募证券基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>郑州市赛迪商贸有限公司</t>
+          <t>深圳市乐禾荷文化实业有限公司</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -6838,7 +6862,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr"/>
@@ -6846,25 +6870,29 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>重庆日邦商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B312" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D312" s="4" t="inlineStr"/>
+          <t>深圳市滨利投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>重庆泰戈新能源发展有限公司</t>
+          <t>深圳市真利视界科技有限公司</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -6874,7 +6902,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr"/>
@@ -6882,25 +6910,29 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>重庆航铝物资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B314" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C314" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D314" s="4" t="inlineStr"/>
+          <t>深圳市鼎泉盛世投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>银河期货有限公司</t>
+          <t>混沌天成期货股份有限公司上海分公司</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -6915,58 +6947,50 @@
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>长安期货有限公司</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C316" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>清河县仟昌商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>长江期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C317" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D317" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>湖南中升物贸有限责任公司</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>长沙市玉阅咨询服务有限公司</t>
+          <t>湖南金润通贸易发展有限公司</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -6976,7 +7000,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr"/>
@@ -6984,7 +7008,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>阿克苏市恒鑫顺调料批发部</t>
+          <t>潍坊方程式生物化工有限公司</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -6994,7 +7018,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr"/>
@@ -7002,29 +7026,25 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>陈荣跃</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>烟台东诚果业有限公司</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>陕西亿佳农牧科技有限公司</t>
+          <t>烟台仕源建筑劳务有限公司</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -7034,7 +7054,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr"/>
@@ -7042,7 +7062,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>隆昌博文视光眼镜有限责任公司</t>
+          <t>牧原食品集团股份有限公司</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -7052,7 +7072,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr"/>
@@ -7060,25 +7080,29 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>青岛信达新材料有限公司</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D323" s="4" t="inlineStr"/>
+          <t>物产中大期货有限公司</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>青岛柏霖农业科技发展有限公司</t>
+          <t>甘肃宇航电力科技有限公司</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -7088,7 +7112,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr"/>
@@ -7096,43 +7120,47 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>青岛金月亮建设工程有限公司</t>
-        </is>
-      </c>
-      <c r="B325" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C325" s="4" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D325" s="4" t="inlineStr"/>
+          <t>甬兴证券有限公司</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>黄梅县泰源棉业有限公司</t>
-        </is>
-      </c>
-      <c r="B326" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C326" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D326" s="4" t="inlineStr"/>
+          <t>百万期货</t>
+        </is>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C326" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D326" s="6" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>黑山县贺兴养殖专业合作社</t>
+          <t>石家庄市北为商业管理有限公司</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -7142,7 +7170,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr"/>
@@ -7150,45 +7178,893 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>黑龙江优上家族投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B328" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C328" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D328" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>石景涛</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
+          <t>磐启国际贸易（北京）有限公司</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>红期分享测试</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>绵阳市乐事多食品有限公司</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>胡洋洋</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>芜湖中铸材料科技有限公司</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>苏州创元和赢资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>苏州创元投资发展（集团）有限公司</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>苏豪弘业期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>营销管理部</t>
+        </is>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C337" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D337" s="6" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>营销管理部</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D338" s="6" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>融创智富（深圳）资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>衡水宝泰机械配件制造有限公司</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>许昌市同庆纺织实业有限公司</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>许昌市建安区天运生猪养殖场</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>诸城市大科建材营销店（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>谷实生物科技（天津）有限公司</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>账号已注销</t>
+        </is>
+      </c>
+      <c r="B345" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C345" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D345" s="6" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>贵州百农汇农业集团有限公司</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>赖永春</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>赣州盈实信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>路源（大连）石化产品有限公司</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>辽宁昊瑞实商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>邢台麦之多商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>邯郸市瑞霞贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B352" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>郁卫华</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>郑州市赛迪商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>重庆日邦商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>重庆航铝物资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>银河期货有限公司</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>长江期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>陈泓霖</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>陈荣跃</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>陕西亿佳农牧科技有限公司</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>陕西宏展农业开发有限公司</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D362" s="4" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>隆昌博文视光眼镜有限责任公司</t>
+        </is>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>青岛信达新材料有限公司</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>青岛柏霖农业科技发展有限公司</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>青岛金月亮建设工程有限公司</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>青岛锦记实业有限公司</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>马玉坤</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D368" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>鸿霆科技（海南）有限公司</t>
+        </is>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>黑山县贺兴养殖专业合作社</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江优上家族投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C371" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
           <t>鼎成纺织（南通）有限公司</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C329" s="4" t="inlineStr">
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr">
         <is>
           <t>制造业</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr"/>
+      <c r="D372" s="4" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>龙口市昱阳食品有限公司</t>
+        </is>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D373" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D329"/>
+  <autoFilter ref="A1:D373"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7231,7 +8107,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
@@ -7241,7 +8117,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
@@ -7251,7 +8127,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -7261,7 +8137,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/客户分类结果.xlsx
+++ b/客户分类结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$329</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D373"/>
+  <dimension ref="A1:D329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海亿衍私募基金管理有限公司</t>
+          <t>上海众壹资产管理有限公司</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -642,60 +642,64 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海冕泓实业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
+          <t>上海八桂资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海双隆投资有限公司</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海冕泓实业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海均元址元文化传媒有限责任公司</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>上海双隆投资有限公司</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -722,7 +726,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海港耀科技有限公司</t>
+          <t>上海河清龙樾企业管理有限公司</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -740,7 +744,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海炫健体育文化传播有限公司</t>
+          <t>上海港耀科技有限公司</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -758,7 +762,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海然盛贸易有限公司</t>
+          <t>上海申袆实业有限公司</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -816,25 +820,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海翔涌化工国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+          <t>上海维万私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海融合良谷供应链有限公司</t>
+          <t>上海翔涌化工国际贸易有限公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -936,46 +944,38 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>东方龙木（海南）国际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>东莞市大岭山赣进粮油经营部</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -2190,7 +2190,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个体期货</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -3202,403 +3202,367 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中信建投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中信期货有限公司</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中原期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中国平安保险（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中基宁波集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中央储备粮辽东湾直属库有限公司</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中泰期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中粮农业产业管理服务有限公司</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中粮期货有限公司</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>中衍期货有限公司</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中间市场部</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>临清市翔茂木材加工厂</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>云南程鹏饲料有限责任公司</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>五矿期货有限公司</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>产品管理部</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>元氏县炜淼农业开发有限公司</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>光大期货有限公司</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>个体期货</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>全国畜牧总站</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>中信建投期货有限公司</t>
+          <t>兴业期货有限公司</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -3620,7 +3584,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>中信期货有限公司</t>
+          <t>兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -3630,19 +3594,19 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>中原期货股份有限公司</t>
+          <t>兴证期货有限公司</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -3664,7 +3628,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>中国供销集团延长果业有限责任公司</t>
+          <t>冀交港口物流唐山有限公司</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -3674,7 +3638,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3682,47 +3646,47 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>中国平安保险（集团）股份有限公司</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>保险集团</t>
-        </is>
-      </c>
+          <t>冠县乐园养殖有限公司</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>中基宁波集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr"/>
+          <t>刘晓明</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>中央储备粮辽东湾直属库有限公司</t>
+          <t>北京六合粮源农业科技有限公司</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -3740,7 +3704,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>中山麦卡迪数码科技有限公司</t>
+          <t>北京国康未来医学研究院</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -3758,127 +3722,123 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>中泰期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京摩卡站餐饮管理有限公司</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>中粮农业产业管理服务有限公司</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>北京星鹏联海私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>中粮期货有限公司</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京永盛芳科贸有限公司</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>中衍期货有限公司</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>北京盛维弘波管理顾问有限公司</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>中间市场部</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
+          <t>北京顶峰时刻科技有限公司</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>云南程鹏饲料有限责任公司</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
+          <t>华安期货有限责任公司青岛营业部</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>五矿期货有限公司</t>
+          <t>华泰期货有限公司</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -3900,25 +3860,29 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>产品管理部</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr"/>
+          <t>华泰期货有限公司上海世纪大道营业部</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>元氏县炜淼农业开发有限公司</t>
+          <t>华裕农业科技有限公司</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -3936,7 +3900,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>光大期货有限公司</t>
+          <t>华闻期货有限公司</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -3958,69 +3922,65 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>全国畜牧总站</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr"/>
+          <t>南京洲利盛科技有限公司</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>兴业期货有限公司</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>南宁市荣泽钢材有限公司</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>证券公司</t>
+          <t>南志云</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>兴证期货有限公司</t>
+          <t>南通中睿投资有限公司</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -4030,19 +3990,19 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>冀交港口物流唐山有限公司</t>
+          <t>南通市崇川区帅昌贸易有限公司</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -4052,7 +4012,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
@@ -4060,7 +4020,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>冠县乐园养殖有限公司</t>
+          <t>南通鸿华化工有限公司</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -4070,7 +4030,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr"/>
@@ -4078,29 +4038,25 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>刘晓明</t>
-        </is>
-      </c>
-      <c r="B168" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>博白县那林镇多福养鸡专业合作社</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>北京六合粮源农业科技有限公司</t>
+          <t>合肥神之手贸易有限公司</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -4110,7 +4066,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr"/>
@@ -4118,51 +4074,47 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>北京厚奕投资有限公司</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>吉林普康农业有限公司</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>北京君和九思私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>周琎</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>北京国康未来医学研究院</t>
+          <t>呼伦贝尔上丰管道有限公司</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -4172,7 +4124,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr"/>
@@ -4180,7 +4132,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>北京摩卡站餐饮管理有限公司</t>
+          <t>哈尔滨领骏商贸有限公司</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -4190,7 +4142,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr"/>
@@ -4198,51 +4150,43 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>北京星鹏联海私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>唐人神集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>北京琮碧秋实私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>唐山市华辉金属制品有限公司</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>北京盛维弘波管理顾问有限公司</t>
+          <t>嘉兴星驰包装材料有限公司</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -4252,7 +4196,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr"/>
@@ -4260,149 +4204,149 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>华安期货有限责任公司青岛营业部</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>嘉吉饲料（天津）有限公司</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>嘉悦物产集团有限公司</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司上海世纪大道营业部</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>四川省乐山市明仕农业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>华裕农业科技有限公司</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr"/>
+          <t>国信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>南京洲利盛科技有限公司</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr"/>
+          <t>国投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>南宁市荣泽钢材有限公司</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr"/>
+          <t>国海良时期货有限公司</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>南志云</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>国联期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>南昌南鲸广告有限公司</t>
+          <t>夏邑县曹集乡华鑫养殖场</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -4412,7 +4356,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr"/>
@@ -4420,7 +4364,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>南通中睿投资有限公司</t>
+          <t>大地期货有限公司</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -4430,19 +4374,19 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>南通市崇川区帅昌贸易有限公司</t>
+          <t>天津北宁科技有限公司</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -4452,7 +4396,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr"/>
@@ -4460,7 +4404,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>南通鸿华化工有限公司</t>
+          <t>宁夏新海恒基贸易有限公司</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -4470,7 +4414,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
@@ -4478,7 +4422,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>博白县那林镇多福养鸡专业合作社</t>
+          <t>宁波市桐易广告影视传媒有限公司</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -4488,7 +4432,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr"/>
@@ -4496,7 +4440,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>合肥神之手贸易有限公司</t>
+          <t>宁波穗淼贸易有限公司</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -4514,25 +4458,29 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>吉林普康农业有限公司</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr"/>
+          <t>宁波静一私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨领骏商贸有限公司</t>
+          <t>安徽骄阳电力科技有限公司</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -4542,7 +4490,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr"/>
@@ -4550,7 +4498,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>唐人神集团股份有限公司</t>
+          <t>安阳国匠环境科技有限公司</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -4560,7 +4508,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr"/>
@@ -4568,61 +4516,73 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>唐山市华辉金属制品有限公司</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>嘉兴星驰包装材料有限公司</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>嘉吉饲料（天津）有限公司</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司广东分公司</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>嘉悦物产集团有限公司</t>
+          <t>宜宾丝丽雅集团有限公司</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -4632,7 +4592,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr"/>
@@ -4640,25 +4600,25 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>四川安卓联商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr"/>
+          <t>富宝账号维护</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>四川成都彭州三电电缆制造有限公司</t>
+          <t>富邦橡胶（浙江）有限公司</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -4676,7 +4636,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>四川省乐山市明仕农业发展有限公司</t>
+          <t>富邦资源控股集团有限公司</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -4686,7 +4646,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr"/>
@@ -4694,29 +4654,25 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>国信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东卓创资讯股份有限公司</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>国华工程科技（集团）有限责任公司</t>
+          <t>山东嘉璐生物科技有限公司</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -4726,7 +4682,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr"/>
@@ -4734,29 +4690,25 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>国投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东成武吉乐原禽业育种有限公司</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>国泰君安期货有限公司深圳福田分公司</t>
+          <t>山东港口投资控股有限公司</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -4766,41 +4718,37 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>期货公司分公司</t>
+          <t>私募投资集团</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>国海良时期货有限公司</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东金工机电工业有限公司</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>国联期货股份有限公司</t>
+          <t>山东齐盛期货有限公司</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -4822,25 +4770,29 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>塞洪（上海）贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D206" s="4" t="inlineStr"/>
+          <t>山东齐盛期货有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>夏邑县曹集乡华鑫养殖场</t>
+          <t>山西鑫辉食品股份有限公司</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -4850,7 +4802,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr"/>
@@ -4858,51 +4810,43 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>大地期货有限公司</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>峨眉山市民生源生态农业科技发展有限公司</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>大地期货有限公司温州分公司</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>常州奕允供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>大连德佰电子商务有限公司</t>
+          <t>广东五湖农业科技有限公司</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -4912,7 +4856,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr"/>
@@ -4920,65 +4864,69 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>天津北宁科技有限公司</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D211" s="4" t="inlineStr"/>
+          <t>广东厚方投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>天津奇略云天科技合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广东嘉誉化工有限公司</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>宁波市桐易广告影视传媒有限公司</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D213" s="4" t="inlineStr"/>
+          <t>广东横琴均成私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>宁波穗淼贸易有限公司</t>
+          <t>广州市佰胜展览服务有限公司</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -4988,7 +4936,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr"/>
@@ -4996,29 +4944,25 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>宁波静一私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广州市嘉玉华粮油贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>安徽和协园艺有限公司</t>
+          <t>广州市天塑塑料制品有限公司</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -5028,7 +4972,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr"/>
@@ -5036,7 +4980,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>安徽省安庆市科大包装材料有限公司</t>
+          <t>广州正鲜农牧科技有限公司</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -5046,7 +4990,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr"/>
@@ -5054,25 +4998,29 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>安徽骄阳电力科技有限公司</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D218" s="4" t="inlineStr"/>
+          <t>广州汇川私募证券投资基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>安阳国匠环境科技有限公司</t>
+          <t>广州泰禾能源有限公司</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -5082,7 +5030,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr"/>
@@ -5090,69 +5038,65 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>广州越秀企业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司广东分公司</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>广西聚则新贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>宜宾丝丽雅集团有限公司</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D222" s="4" t="inlineStr"/>
+          <t>建信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>宿州市隆润农牧有限公司</t>
+          <t>徐州好益佳食品有限公司</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -5162,7 +5106,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -5170,25 +5114,29 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>富宝账号维护</t>
-        </is>
-      </c>
-      <c r="B224" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C224" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D224" s="6" t="inlineStr"/>
+          <t>徽商期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>富邦资源控股集团有限公司</t>
+          <t>惠州市小象智能科技有限公司</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -5198,7 +5146,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr"/>
@@ -5206,7 +5154,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>山东嘉璐生物科技有限公司</t>
+          <t>成都世纪昊天商贸有限公司</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -5216,7 +5164,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr"/>
@@ -5224,7 +5172,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>山东成武吉乐原禽业育种有限公司</t>
+          <t>成都岭南春商贸有限公司</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -5234,7 +5182,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr"/>
@@ -5242,61 +5190,73 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>山东智义恒商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr"/>
+          <t>招商期货有限公司</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>山东祖豪物流有限公司</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr"/>
+          <t>敦和资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>山东金工机电工业有限公司</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr"/>
+          <t>新湖期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司</t>
+          <t>方正中期期货有限公司</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -5318,7 +5278,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司福建分公司</t>
+          <t>方正证券股份有限公司</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -5328,19 +5288,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>期货公司分公司</t>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>山西鑫辉食品股份有限公司</t>
+          <t>日照泰高亚昊饲料科技有限公司</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -5350,7 +5310,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr"/>
@@ -5358,7 +5318,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>常州铭梵环境咨询有限公司</t>
+          <t>昆山民巨电子科技有限公司</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -5368,7 +5328,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr"/>
@@ -5376,7 +5336,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>广东五湖农业科技有限公司</t>
+          <t>昆山玉高精密设备有限公司</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -5386,7 +5346,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr"/>
@@ -5394,7 +5354,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>广东厚方投资管理有限公司</t>
+          <t>易持（厦门）私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -5416,25 +5376,29 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>广东嘉誉化工有限公司</t>
-        </is>
-      </c>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C237" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D237" s="4" t="inlineStr"/>
+          <t>李平野</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>广东横琴均成私募基金管理有限公司</t>
+          <t>杭州孚盈投资管理有限公司</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -5456,25 +5420,29 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>广州华创山海贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D239" s="4" t="inlineStr"/>
+          <t>杭州山量投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>广州市嘉玉华粮油贸易有限公司</t>
+          <t>杭州朝霞实业有限公司</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -5484,7 +5452,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr"/>
@@ -5492,7 +5460,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>广州市天塑塑料制品有限公司</t>
+          <t>杭州纳永实业有限公司</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -5502,7 +5470,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr"/>
@@ -5510,25 +5478,29 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>广州正鲜农牧科技有限公司</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr"/>
+          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>广州汇川私募证券投资基金管理有限公司</t>
+          <t>格林大华期货有限公司</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -5538,77 +5510,81 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>广州越秀企业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr"/>
+          <t>正信期货有限公司</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>广西聚则新贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr"/>
+          <t>武汉市钧凌实业投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>建信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>武汉数商科技有限公司</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>张家港市星恒工具有限公司</t>
+          <t>武汉苍鹰贸易有限公司</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -5618,7 +5594,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr"/>
@@ -5626,47 +5602,47 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>徐州好益佳食品有限公司</t>
-        </is>
-      </c>
-      <c r="B248" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C248" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr"/>
+          <t>永安期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>徽商期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C249" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>永富物产有限公司</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>惠州市小象智能科技有限公司</t>
+          <t>永康市浩资建筑材料厂</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -5676,7 +5652,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr"/>
@@ -5684,25 +5660,29 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>成都世纪昊天商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr"/>
+          <t>汇丰前海证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>外资券商</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>成都岭南春商贸有限公司</t>
+          <t>汕头市诚兴塑化有限公司</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -5720,29 +5700,25 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>房兴旭</t>
-        </is>
-      </c>
-      <c r="B253" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C253" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>江山市永丰化建有限公司</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>招商期货有限公司</t>
+          <t>江海汇鑫期货有限公司</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -5764,7 +5740,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>新享数成（济南）数字科技有限公司</t>
+          <t>江西国元农业发展集团有限公司</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -5774,7 +5750,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr"/>
@@ -5782,29 +5758,25 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>新湖期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>河北卓峰化肥有限公司</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>新疆融创汇欣物产农业有限责任公司</t>
+          <t>河北古月坊农业科技有限公司</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -5814,7 +5786,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr"/>
@@ -5822,51 +5794,43 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>方正中期期货有限公司</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>河南君友商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>方正证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C259" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>河南省才聚万锦生猪贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>日照泰高亚昊饲料科技有限公司</t>
+          <t>河南金之晟养殖有限公司</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -5884,7 +5848,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>昆山民巨电子科技有限公司</t>
+          <t>河南鑫诺农业发展有限公司</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -5894,7 +5858,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr"/>
@@ -5902,29 +5866,25 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>易持（厦门）私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D262" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>泉州市润心塑胶科技有限公司</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>曹县砖庙镇凯悦养殖场</t>
+          <t>泰安市泰山区海阔饲料销售中心</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -5942,47 +5902,51 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
+          <t>浙商期货有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="B264" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C264" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D264" s="6" t="inlineStr"/>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>李平野</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>浙江南华资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>杭州孚盈投资管理有限公司</t>
+          <t>浙江新世纪期货有限公司</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -5992,41 +5956,37 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>杭州山量投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>浙江旺璐物资有限公司</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>杭州朝霞实业有限公司</t>
+          <t>浙江杭实善成实业有限公司</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -6036,7 +5996,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr"/>
@@ -6044,87 +6004,87 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>杭州纳永实业有限公司</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D269" s="4" t="inlineStr"/>
+          <t>浙江金榕树投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>杭州花生壳科技有限公司</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D270" s="4" t="inlineStr"/>
+          <t>海南佳岳私募证券基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>海南农垦草畜猪业有限公司</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>格林大华期货有限公司</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>海宁帕提时尚服饰有限公司</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>正信期货有限公司</t>
+          <t>海通期货股份有限公司</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -6146,29 +6106,25 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>武汉市钧凌实业投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>淄博市多盈数据智能有限公司</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>武汉数商科技有限公司</t>
+          <t>深圳市兵法技术有限公司</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -6186,7 +6142,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>武汉苍鹰贸易有限公司</t>
+          <t>深圳市慧网第三方信息咨询有限公司</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -6196,7 +6152,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr"/>
@@ -6204,29 +6160,25 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>永安期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D277" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>深圳市汇淼淼贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>永康市浩资建筑材料厂</t>
+          <t>深圳市真利视界科技有限公司</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -6236,7 +6188,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr"/>
@@ -6244,7 +6196,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>汇丰前海证券有限责任公司</t>
+          <t>深圳市鼎泉盛世投资管理有限公司</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -6254,37 +6206,41 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>外资券商</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>汕头市诚兴塑化有限公司</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D280" s="4" t="inlineStr"/>
+          <t>混沌天成期货股份有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>江山市永丰化建有限公司</t>
+          <t>湖南中升物贸有限责任公司</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -6302,29 +6258,25 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>江海汇鑫期货有限公司</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C282" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>潍坊方程式生物化工有限公司</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>江西中啟建设工程有限公司</t>
+          <t>烟台东诚果业有限公司</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -6334,7 +6286,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr"/>
@@ -6342,7 +6294,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>江西国元农业发展集团有限公司</t>
+          <t>牧原食品集团股份有限公司</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -6360,115 +6312,131 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>江西状元郎食品集团有限公司</t>
-        </is>
-      </c>
-      <c r="B285" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D285" s="4" t="inlineStr"/>
+          <t>物产中大期货有限公司</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>河北卓峰化肥有限公司</t>
-        </is>
-      </c>
-      <c r="B286" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D286" s="4" t="inlineStr"/>
+          <t>王斌华</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>河北古月坊农业科技有限公司</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D287" s="4" t="inlineStr"/>
+          <t>王绎翔</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>河南君友商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C288" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D288" s="4" t="inlineStr"/>
+          <t>百万期货</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D288" s="6" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>河南省冠林贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B289" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C289" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D289" s="4" t="inlineStr"/>
+          <t>石景涛</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>河南省才聚万锦生猪贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C290" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D290" s="4" t="inlineStr"/>
+          <t>红期分享测试</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D290" s="6" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>河南金之晟养殖有限公司</t>
+          <t>绵阳市乐事多食品有限公司</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -6478,7 +6446,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr"/>
@@ -6486,25 +6454,29 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>河南鑫诺农业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B292" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C292" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D292" s="4" t="inlineStr"/>
+          <t>胡洋洋</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>泉州市润心塑胶科技有限公司</t>
+          <t>芜湖中铸材料科技有限公司</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -6522,7 +6494,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>泰安市泰山区海阔饲料销售中心</t>
+          <t>苏州万家鲜食品有限公司</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -6532,7 +6504,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr"/>
@@ -6540,43 +6512,51 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>济宁市明辰木业有限公司</t>
-        </is>
-      </c>
-      <c r="B295" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C295" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D295" s="4" t="inlineStr"/>
+          <t>苏州创元和赢资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>浙商中拓集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B296" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C296" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D296" s="4" t="inlineStr"/>
+          <t>苏州创元投资发展（集团）有限公司</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>浙商期货有限公司上海分公司</t>
+          <t>苏豪弘业期货股份有限公司</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -6591,14 +6571,14 @@
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>期货公司分公司</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>浙江华道律师事务所</t>
+          <t>蔚县怡洲商贸有限公司</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -6608,7 +6588,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr"/>
@@ -6616,47 +6596,47 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>浙江卓诗尼鞋业有限公司</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D299" s="4" t="inlineStr"/>
+          <t>融创智富（深圳）资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>浙江南华资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C300" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D300" s="3" t="inlineStr">
-        <is>
-          <t>券商私募（另类投资）</t>
-        </is>
-      </c>
+          <t>衡水宝泰机械配件制造有限公司</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>浙江响农农副产品有限公司</t>
+          <t>许昌市同庆纺织实业有限公司</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -6666,7 +6646,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr"/>
@@ -6674,29 +6654,29 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>浙江新世纪期货有限公司</t>
-        </is>
-      </c>
-      <c r="B302" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C302" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D302" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>诸城市大科建材营销店（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>浙江旺璐物资有限公司</t>
+          <t>谷实生物科技（天津）有限公司</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -6706,7 +6686,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr"/>
@@ -6714,65 +6694,65 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>浙江杭实善成实业有限公司</t>
-        </is>
-      </c>
-      <c r="B304" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C304" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D304" s="4" t="inlineStr"/>
+          <t>账号已注销</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C304" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D304" s="6" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>海南佳岳私募证券基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C305" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D305" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>贵州百农汇农业集团有限公司</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>海南农垦草畜猪业有限公司</t>
-        </is>
-      </c>
-      <c r="B306" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C306" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D306" s="4" t="inlineStr"/>
+          <t>贵阳新泰投资有限公司</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>海宁帕提时尚服饰有限公司</t>
+          <t>赣州盈实信息科技有限公司</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -6782,7 +6762,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr"/>
@@ -6790,29 +6770,25 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>海通期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B308" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C308" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D308" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>路源（大连）石化产品有限公司</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>淄博市多盈数据智能有限公司</t>
+          <t>邢台麦之多商贸有限公司</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -6822,7 +6798,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr"/>
@@ -6830,29 +6806,29 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>深圳中盈蓝景私募证券基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B310" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C310" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D310" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>郁卫华</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>深圳市乐禾荷文化实业有限公司</t>
+          <t>郑州市赛迪商贸有限公司</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -6862,7 +6838,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr"/>
@@ -6870,29 +6846,25 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>深圳市滨利投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C312" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D312" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>重庆日邦商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>深圳市真利视界科技有限公司</t>
+          <t>重庆泰戈新能源发展有限公司</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -6902,7 +6874,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr"/>
@@ -6910,29 +6882,25 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>深圳市鼎泉盛世投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D314" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>重庆航铝物资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>混沌天成期货股份有限公司上海分公司</t>
+          <t>银河期货有限公司</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -6947,50 +6915,58 @@
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>期货公司分公司</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>清河县仟昌商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B316" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C316" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D316" s="4" t="inlineStr"/>
+          <t>长安期货有限公司</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>湖南中升物贸有限责任公司</t>
-        </is>
-      </c>
-      <c r="B317" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C317" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D317" s="4" t="inlineStr"/>
+          <t>长江期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>湖南金润通贸易发展有限公司</t>
+          <t>长沙市玉阅咨询服务有限公司</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -7000,7 +6976,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr"/>
@@ -7008,7 +6984,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>潍坊方程式生物化工有限公司</t>
+          <t>阿克苏市恒鑫顺调料批发部</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -7018,7 +6994,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr"/>
@@ -7026,25 +7002,29 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>烟台东诚果业有限公司</t>
-        </is>
-      </c>
-      <c r="B320" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C320" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D320" s="4" t="inlineStr"/>
+          <t>陈荣跃</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>烟台仕源建筑劳务有限公司</t>
+          <t>陕西亿佳农牧科技有限公司</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -7054,7 +7034,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr"/>
@@ -7062,7 +7042,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>牧原食品集团股份有限公司</t>
+          <t>隆昌博文视光眼镜有限责任公司</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -7072,7 +7052,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr"/>
@@ -7080,29 +7060,25 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>物产中大期货有限公司</t>
-        </is>
-      </c>
-      <c r="B323" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C323" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D323" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>青岛信达新材料有限公司</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>甘肃宇航电力科技有限公司</t>
+          <t>青岛柏霖农业科技发展有限公司</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -7112,7 +7088,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr"/>
@@ -7120,47 +7096,43 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>甬兴证券有限公司</t>
-        </is>
-      </c>
-      <c r="B325" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C325" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D325" s="3" t="inlineStr">
-        <is>
-          <t>证券公司</t>
-        </is>
-      </c>
+          <t>青岛金月亮建设工程有限公司</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>百万期货</t>
-        </is>
-      </c>
-      <c r="B326" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C326" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D326" s="6" t="inlineStr"/>
+          <t>黄梅县泰源棉业有限公司</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>石家庄市北为商业管理有限公司</t>
+          <t>黑山县贺兴养殖专业合作社</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -7170,7 +7142,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr"/>
@@ -7178,29 +7150,29 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>石景涛</t>
-        </is>
-      </c>
-      <c r="B328" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C328" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D328" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>黑龙江优上家族投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>磐启国际贸易（北京）有限公司</t>
+          <t>鼎成纺织（南通）有限公司</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
@@ -7210,861 +7182,13 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr"/>
     </row>
-    <row r="330">
-      <c r="A330" s="2" t="inlineStr">
-        <is>
-          <t>红期分享测试</t>
-        </is>
-      </c>
-      <c r="B330" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C330" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D330" s="6" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>绵阳市乐事多食品有限公司</t>
-        </is>
-      </c>
-      <c r="B331" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C331" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D331" s="4" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>胡洋洋</t>
-        </is>
-      </c>
-      <c r="B332" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C332" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D332" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="inlineStr">
-        <is>
-          <t>芜湖中铸材料科技有限公司</t>
-        </is>
-      </c>
-      <c r="B333" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D333" s="4" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>苏州创元和赢资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C334" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D334" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>苏州创元投资发展（集团）有限公司</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C335" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>苏豪弘业期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D336" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>营销管理部</t>
-        </is>
-      </c>
-      <c r="B337" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C337" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D337" s="6" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>营销管理部</t>
-        </is>
-      </c>
-      <c r="B338" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C338" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D338" s="6" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>融创智富（深圳）资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C339" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D339" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>衡水宝泰机械配件制造有限公司</t>
-        </is>
-      </c>
-      <c r="B340" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D340" s="4" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>许昌市同庆纺织实业有限公司</t>
-        </is>
-      </c>
-      <c r="B341" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D341" s="4" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>许昌市建安区天运生猪养殖场</t>
-        </is>
-      </c>
-      <c r="B342" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D342" s="4" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>诸城市大科建材营销店（个体工商户）</t>
-        </is>
-      </c>
-      <c r="B343" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C343" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D343" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="inlineStr">
-        <is>
-          <t>谷实生物科技（天津）有限公司</t>
-        </is>
-      </c>
-      <c r="B344" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C344" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D344" s="4" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="inlineStr">
-        <is>
-          <t>账号已注销</t>
-        </is>
-      </c>
-      <c r="B345" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C345" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D345" s="6" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>贵州百农汇农业集团有限公司</t>
-        </is>
-      </c>
-      <c r="B346" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C346" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D346" s="4" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="inlineStr">
-        <is>
-          <t>赖永春</t>
-        </is>
-      </c>
-      <c r="B347" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C347" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D347" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>赣州盈实信息科技有限公司</t>
-        </is>
-      </c>
-      <c r="B348" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C348" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D348" s="4" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>路源（大连）石化产品有限公司</t>
-        </is>
-      </c>
-      <c r="B349" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C349" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D349" s="4" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>辽宁昊瑞实商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B350" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D350" s="4" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>邢台麦之多商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B351" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C351" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D351" s="4" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>邯郸市瑞霞贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B352" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C352" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D352" s="4" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>郁卫华</t>
-        </is>
-      </c>
-      <c r="B353" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C353" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D353" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>郑州市赛迪商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B354" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C354" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D354" s="4" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>重庆日邦商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B355" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C355" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D355" s="4" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="inlineStr">
-        <is>
-          <t>重庆航铝物资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B356" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C356" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D356" s="4" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>银河期货有限公司</t>
-        </is>
-      </c>
-      <c r="B357" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C357" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D357" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="inlineStr">
-        <is>
-          <t>长江期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B358" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C358" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D358" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>陈泓霖</t>
-        </is>
-      </c>
-      <c r="B359" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C359" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D359" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="2" t="inlineStr">
-        <is>
-          <t>陈荣跃</t>
-        </is>
-      </c>
-      <c r="B360" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C360" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D360" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="2" t="inlineStr">
-        <is>
-          <t>陕西亿佳农牧科技有限公司</t>
-        </is>
-      </c>
-      <c r="B361" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C361" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D361" s="4" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="2" t="inlineStr">
-        <is>
-          <t>陕西宏展农业开发有限公司</t>
-        </is>
-      </c>
-      <c r="B362" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C362" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D362" s="4" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="2" t="inlineStr">
-        <is>
-          <t>隆昌博文视光眼镜有限责任公司</t>
-        </is>
-      </c>
-      <c r="B363" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C363" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D363" s="4" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" s="2" t="inlineStr">
-        <is>
-          <t>青岛信达新材料有限公司</t>
-        </is>
-      </c>
-      <c r="B364" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C364" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D364" s="4" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" s="2" t="inlineStr">
-        <is>
-          <t>青岛柏霖农业科技发展有限公司</t>
-        </is>
-      </c>
-      <c r="B365" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C365" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D365" s="4" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" s="2" t="inlineStr">
-        <is>
-          <t>青岛金月亮建设工程有限公司</t>
-        </is>
-      </c>
-      <c r="B366" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C366" s="4" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D366" s="4" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="2" t="inlineStr">
-        <is>
-          <t>青岛锦记实业有限公司</t>
-        </is>
-      </c>
-      <c r="B367" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C367" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D367" s="4" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="2" t="inlineStr">
-        <is>
-          <t>马玉坤</t>
-        </is>
-      </c>
-      <c r="B368" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C368" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D368" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="2" t="inlineStr">
-        <is>
-          <t>鸿霆科技（海南）有限公司</t>
-        </is>
-      </c>
-      <c r="B369" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C369" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D369" s="4" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="2" t="inlineStr">
-        <is>
-          <t>黑山县贺兴养殖专业合作社</t>
-        </is>
-      </c>
-      <c r="B370" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C370" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D370" s="4" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>黑龙江优上家族投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B371" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C371" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D371" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="2" t="inlineStr">
-        <is>
-          <t>鼎成纺织（南通）有限公司</t>
-        </is>
-      </c>
-      <c r="B372" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C372" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D372" s="4" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="2" t="inlineStr">
-        <is>
-          <t>龙口市昱阳食品有限公司</t>
-        </is>
-      </c>
-      <c r="B373" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D373" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D373"/>
+  <autoFilter ref="A1:D329"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8107,7 +7231,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
@@ -8117,7 +7241,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -8127,7 +7251,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -8137,7 +7261,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>372</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/客户分类结果.xlsx
+++ b/客户分类结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分类汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户分类'!$A$1:$D$373</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D329"/>
+  <dimension ref="A1:D373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海众壹资产管理有限公司</t>
+          <t>上海亿衍私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -642,64 +642,60 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海八桂资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海冕泓实业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海冕泓实业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+          <t>上海双隆投资有限公司</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海双隆投资有限公司</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海均元址元文化传媒有限责任公司</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海河清龙樾企业管理有限公司</t>
+          <t>上海港耀科技有限公司</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -744,7 +740,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海港耀科技有限公司</t>
+          <t>上海炫健体育文化传播有限公司</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -762,7 +758,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海申袆实业有限公司</t>
+          <t>上海然盛贸易有限公司</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -820,29 +816,25 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海维万私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>上海翔涌化工国际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海翔涌化工国际贸易有限公司</t>
+          <t>上海融合良谷供应链有限公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -852,7 +844,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -944,38 +936,46 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>东方龙木（海南）国际贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>东莞市大岭山赣进粮油经营部</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -2190,7 +2190,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>个体</t>
+          <t>个人</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>个体期货</t>
+          <t>个体</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -3202,367 +3202,403 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>中信建投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>中信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>中原期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>中国平安保险（集团）股份有限公司</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>保险集团</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>中基宁波集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>中央储备粮辽东湾直属库有限公司</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>中泰期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>中粮农业产业管理服务有限公司</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>中粮期货有限公司</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>中衍期货有限公司</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>中间市场部</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>临清市翔茂木材加工厂</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>云南程鹏饲料有限责任公司</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>五矿期货有限公司</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>产品管理部</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>元氏县炜淼农业开发有限公司</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr"/>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>光大期货有限公司</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>个体</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>全国畜牧总站</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr"/>
+          <t>个体期货</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>兴业期货有限公司</t>
+          <t>中信建投期货有限公司</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -3584,7 +3620,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
+          <t>中信期货有限公司</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -3594,19 +3630,19 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>证券公司</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>兴证期货有限公司</t>
+          <t>中原期货股份有限公司</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -3628,7 +3664,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>冀交港口物流唐山有限公司</t>
+          <t>中国供销集团延长果业有限责任公司</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -3638,7 +3674,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3646,47 +3682,47 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>冠县乐园养殖有限公司</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>中国平安保险（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>保险集团</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>刘晓明</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>中基宁波集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>北京六合粮源农业科技有限公司</t>
+          <t>中央储备粮辽东湾直属库有限公司</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -3704,7 +3740,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>北京国康未来医学研究院</t>
+          <t>中山麦卡迪数码科技有限公司</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -3722,123 +3758,127 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>北京摩卡站餐饮管理有限公司</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
+          <t>中泰期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>北京星鹏联海私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>中粮农业产业管理服务有限公司</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>北京永盛芳科贸有限公司</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr"/>
+          <t>中粮期货有限公司</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>北京盛维弘波管理顾问有限公司</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>中衍期货有限公司</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>北京顶峰时刻科技有限公司</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr"/>
+          <t>中间市场部</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>华安期货有限责任公司青岛营业部</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>云南程鹏饲料有限责任公司</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司</t>
+          <t>五矿期货有限公司</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -3860,29 +3900,25 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>华泰期货有限公司上海世纪大道营业部</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>产品管理部</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>华裕农业科技有限公司</t>
+          <t>元氏县炜淼农业开发有限公司</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -3900,7 +3936,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>华闻期货有限公司</t>
+          <t>光大期货有限公司</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -3922,65 +3958,69 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>南京洲利盛科技有限公司</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr"/>
+          <t>全国畜牧总站</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>南宁市荣泽钢材有限公司</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr"/>
+          <t>兴业期货有限公司</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>南志云</t>
-        </is>
-      </c>
-      <c r="B164" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D164" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>南通中睿投资有限公司</t>
+          <t>兴证期货有限公司</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -3990,19 +4030,19 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>南通市崇川区帅昌贸易有限公司</t>
+          <t>冀交港口物流唐山有限公司</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -4012,7 +4052,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
@@ -4020,7 +4060,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>南通鸿华化工有限公司</t>
+          <t>冠县乐园养殖有限公司</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -4030,7 +4070,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr"/>
@@ -4038,25 +4078,29 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>博白县那林镇多福养鸡专业合作社</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr"/>
+          <t>刘晓明</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>合肥神之手贸易有限公司</t>
+          <t>北京六合粮源农业科技有限公司</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -4066,7 +4110,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr"/>
@@ -4074,47 +4118,51 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>吉林普康农业有限公司</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr"/>
+          <t>北京厚奕投资有限公司</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>周琎</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>北京君和九思私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>呼伦贝尔上丰管道有限公司</t>
+          <t>北京国康未来医学研究院</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -4124,7 +4172,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr"/>
@@ -4132,7 +4180,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨领骏商贸有限公司</t>
+          <t>北京摩卡站餐饮管理有限公司</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -4142,7 +4190,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr"/>
@@ -4150,43 +4198,51 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>唐人神集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr"/>
+          <t>北京星鹏联海私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>唐山市华辉金属制品有限公司</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr"/>
+          <t>北京琮碧秋实私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>嘉兴星驰包装材料有限公司</t>
+          <t>北京盛维弘波管理顾问有限公司</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -4196,7 +4252,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr"/>
@@ -4204,149 +4260,149 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>嘉吉饲料（天津）有限公司</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr"/>
+          <t>华安期货有限责任公司青岛营业部</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>嘉悦物产集团有限公司</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
+          <t>华泰期货有限公司</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>四川省乐山市明仕农业发展有限公司</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr"/>
+          <t>华泰期货有限公司上海世纪大道营业部</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>国信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>华裕农业科技有限公司</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>国投期货有限公司</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>南京洲利盛科技有限公司</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>国海良时期货有限公司</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>南宁市荣泽钢材有限公司</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>国联期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
+          <t>南志云</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>夏邑县曹集乡华鑫养殖场</t>
+          <t>南昌南鲸广告有限公司</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -4356,7 +4412,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr"/>
@@ -4364,7 +4420,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>大地期货有限公司</t>
+          <t>南通中睿投资有限公司</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -4374,19 +4430,19 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>天津北宁科技有限公司</t>
+          <t>南通市崇川区帅昌贸易有限公司</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -4396,7 +4452,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr"/>
@@ -4404,7 +4460,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>宁夏新海恒基贸易有限公司</t>
+          <t>南通鸿华化工有限公司</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -4414,7 +4470,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
@@ -4422,7 +4478,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>宁波市桐易广告影视传媒有限公司</t>
+          <t>博白县那林镇多福养鸡专业合作社</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -4432,7 +4488,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr"/>
@@ -4440,7 +4496,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>宁波穗淼贸易有限公司</t>
+          <t>合肥神之手贸易有限公司</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -4458,29 +4514,25 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>宁波静一私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>吉林普康农业有限公司</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>安徽骄阳电力科技有限公司</t>
+          <t>哈尔滨领骏商贸有限公司</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -4490,7 +4542,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr"/>
@@ -4498,7 +4550,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>安阳国匠环境科技有限公司</t>
+          <t>唐人神集团股份有限公司</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -4508,7 +4560,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr"/>
@@ -4516,73 +4568,61 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>唐山市华辉金属制品有限公司</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>嘉兴星驰包装材料有限公司</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>宏源期货有限公司广东分公司</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>嘉吉饲料（天津）有限公司</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>宜宾丝丽雅集团有限公司</t>
+          <t>嘉悦物产集团有限公司</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -4592,7 +4632,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr"/>
@@ -4600,25 +4640,25 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>富宝账号维护</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D197" s="6" t="inlineStr"/>
+          <t>四川安卓联商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>富邦橡胶（浙江）有限公司</t>
+          <t>四川成都彭州三电电缆制造有限公司</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -4636,7 +4676,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>富邦资源控股集团有限公司</t>
+          <t>四川省乐山市明仕农业发展有限公司</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -4646,7 +4686,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr"/>
@@ -4654,25 +4694,29 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>山东卓创资讯股份有限公司</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr"/>
+          <t>国信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>山东嘉璐生物科技有限公司</t>
+          <t>国华工程科技（集团）有限责任公司</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -4682,7 +4726,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr"/>
@@ -4690,25 +4734,29 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>山东成武吉乐原禽业育种有限公司</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="inlineStr"/>
+          <t>国投期货有限公司</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>山东港口投资控股有限公司</t>
+          <t>国泰君安期货有限公司深圳福田分公司</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -4718,37 +4766,41 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>私募投资集团</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>山东金工机电工业有限公司</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr"/>
+          <t>国海良时期货有限公司</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司</t>
+          <t>国联期货股份有限公司</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -4770,29 +4822,25 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>山东齐盛期货有限公司福建分公司</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>塞洪（上海）贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>山西鑫辉食品股份有限公司</t>
+          <t>夏邑县曹集乡华鑫养殖场</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -4802,7 +4850,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr"/>
@@ -4810,43 +4858,51 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>峨眉山市民生源生态农业科技发展有限公司</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr"/>
+          <t>大地期货有限公司</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>常州奕允供应链管理有限公司</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr"/>
+          <t>大地期货有限公司温州分公司</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>广东五湖农业科技有限公司</t>
+          <t>大连德佰电子商务有限公司</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -4856,7 +4912,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr"/>
@@ -4864,69 +4920,65 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>广东厚方投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>天津北宁科技有限公司</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>广东嘉誉化工有限公司</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D212" s="4" t="inlineStr"/>
+          <t>天津奇略云天科技合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>广东横琴均成私募基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>宁波市桐易广告影视传媒有限公司</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>广州市佰胜展览服务有限公司</t>
+          <t>宁波穗淼贸易有限公司</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -4936,7 +4988,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr"/>
@@ -4944,25 +4996,29 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>广州市嘉玉华粮油贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="inlineStr"/>
+          <t>宁波静一私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>广州市天塑塑料制品有限公司</t>
+          <t>安徽和协园艺有限公司</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -4972,7 +5028,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr"/>
@@ -4980,7 +5036,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>广州正鲜农牧科技有限公司</t>
+          <t>安徽省安庆市科大包装材料有限公司</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -4990,7 +5046,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr"/>
@@ -4998,29 +5054,25 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>广州汇川私募证券投资基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>安徽骄阳电力科技有限公司</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>广州泰禾能源有限公司</t>
+          <t>安阳国匠环境科技有限公司</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -5030,7 +5082,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr"/>
@@ -5038,65 +5090,69 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>广州越秀企业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>广西聚则新贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr"/>
+          <t>宏源期货有限公司广东分公司</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>期货公司分公司</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>建信期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>宜宾丝丽雅集团有限公司</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>徐州好益佳食品有限公司</t>
+          <t>宿州市隆润农牧有限公司</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -5106,7 +5162,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
@@ -5114,29 +5170,25 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>徽商期货有限责任公司</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>富宝账号维护</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>惠州市小象智能科技有限公司</t>
+          <t>富邦资源控股集团有限公司</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -5146,7 +5198,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr"/>
@@ -5154,7 +5206,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>成都世纪昊天商贸有限公司</t>
+          <t>山东嘉璐生物科技有限公司</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -5164,7 +5216,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr"/>
@@ -5172,7 +5224,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>成都岭南春商贸有限公司</t>
+          <t>山东成武吉乐原禽业育种有限公司</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -5182,7 +5234,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr"/>
@@ -5190,73 +5242,61 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>招商期货有限公司</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东智义恒商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>敦和资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>山东祖豪物流有限公司</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>新湖期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>山东金工机电工业有限公司</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>方正中期期货有限公司</t>
+          <t>山东齐盛期货有限公司</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -5278,7 +5318,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>方正证券股份有限公司</t>
+          <t>山东齐盛期货有限公司福建分公司</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -5288,19 +5328,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>期货</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>证券公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>日照泰高亚昊饲料科技有限公司</t>
+          <t>山西鑫辉食品股份有限公司</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -5310,7 +5350,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr"/>
@@ -5318,7 +5358,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>昆山民巨电子科技有限公司</t>
+          <t>常州铭梵环境咨询有限公司</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -5328,7 +5368,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr"/>
@@ -5336,7 +5376,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>昆山玉高精密设备有限公司</t>
+          <t>广东五湖农业科技有限公司</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -5346,7 +5386,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr"/>
@@ -5354,7 +5394,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>易持（厦门）私募基金管理有限公司</t>
+          <t>广东厚方投资管理有限公司</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -5376,29 +5416,25 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>李平野</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>广东嘉誉化工有限公司</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>杭州孚盈投资管理有限公司</t>
+          <t>广东横琴均成私募基金管理有限公司</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -5420,29 +5456,25 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>杭州山量投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C239" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广州华创山海贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>杭州朝霞实业有限公司</t>
+          <t>广州市嘉玉华粮油贸易有限公司</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -5452,7 +5484,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr"/>
@@ -5460,7 +5492,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>杭州纳永实业有限公司</t>
+          <t>广州市天塑塑料制品有限公司</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -5470,7 +5502,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr"/>
@@ -5478,29 +5510,25 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>广州正鲜农牧科技有限公司</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>格林大华期货有限公司</t>
+          <t>广州汇川私募证券投资基金管理有限公司</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -5510,81 +5538,77 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>正信期货有限公司</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>广州越秀企业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>武汉市钧凌实业投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C245" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>广西聚则新贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>武汉数商科技有限公司</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr"/>
+          <t>建信期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>武汉苍鹰贸易有限公司</t>
+          <t>张家港市星恒工具有限公司</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -5594,7 +5618,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr"/>
@@ -5602,47 +5626,47 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>永安期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>徐州好益佳食品有限公司</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>永富物产有限公司</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D249" s="4" t="inlineStr"/>
+          <t>徽商期货有限责任公司</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>永康市浩资建筑材料厂</t>
+          <t>惠州市小象智能科技有限公司</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -5652,7 +5676,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr"/>
@@ -5660,29 +5684,25 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>汇丰前海证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>外资券商</t>
-        </is>
-      </c>
+          <t>成都世纪昊天商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>汕头市诚兴塑化有限公司</t>
+          <t>成都岭南春商贸有限公司</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -5700,25 +5720,29 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>江山市永丰化建有限公司</t>
-        </is>
-      </c>
-      <c r="B253" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="inlineStr"/>
+          <t>房兴旭</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>江海汇鑫期货有限公司</t>
+          <t>招商期货有限公司</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -5740,7 +5764,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>江西国元农业发展集团有限公司</t>
+          <t>新享数成（济南）数字科技有限公司</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -5750,7 +5774,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr"/>
@@ -5758,25 +5782,29 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>河北卓峰化肥有限公司</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr"/>
+          <t>新湖期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>河北古月坊农业科技有限公司</t>
+          <t>新疆融创汇欣物产农业有限责任公司</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -5786,7 +5814,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr"/>
@@ -5794,43 +5822,51 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>河南君友商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr"/>
+          <t>方正中期期货有限公司</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>河南省才聚万锦生猪贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr"/>
+          <t>方正证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>河南金之晟养殖有限公司</t>
+          <t>日照泰高亚昊饲料科技有限公司</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -5848,7 +5884,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>河南鑫诺农业发展有限公司</t>
+          <t>昆山民巨电子科技有限公司</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -5858,7 +5894,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr"/>
@@ -5866,25 +5902,29 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>泉州市润心塑胶科技有限公司</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D262" s="4" t="inlineStr"/>
+          <t>易持（厦门）私募基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>泰安市泰山区海阔饲料销售中心</t>
+          <t>曹县砖庙镇凯悦养殖场</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -5902,51 +5942,51 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>浙商期货有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
           <t>期货</t>
         </is>
       </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>浙江南华资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>券商私募（另类投资）</t>
+          <t>李平野</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>浙江新世纪期货有限公司</t>
+          <t>杭州孚盈投资管理有限公司</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -5956,37 +5996,41 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>期货</t>
+          <t>基金</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>浙江旺璐物资有限公司</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D267" s="4" t="inlineStr"/>
+          <t>杭州山量投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>浙江杭实善成实业有限公司</t>
+          <t>杭州朝霞实业有限公司</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -5996,7 +6040,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr"/>
@@ -6004,87 +6048,87 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>浙江金榕树投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>杭州纳永实业有限公司</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>海南佳岳私募证券基金管理有限公司</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>杭州花生壳科技有限公司</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>海南农垦草畜猪业有限公司</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D271" s="4" t="inlineStr"/>
+          <t>栖霞区帆科信息咨询工作室（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>海宁帕提时尚服饰有限公司</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D272" s="4" t="inlineStr"/>
+          <t>格林大华期货有限公司</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>海通期货股份有限公司</t>
+          <t>正信期货有限公司</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -6106,25 +6150,29 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>淄博市多盈数据智能有限公司</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>服务业</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr"/>
+          <t>武汉市钧凌实业投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>深圳市兵法技术有限公司</t>
+          <t>武汉数商科技有限公司</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -6142,7 +6190,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>深圳市慧网第三方信息咨询有限公司</t>
+          <t>武汉苍鹰贸易有限公司</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -6152,7 +6200,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr"/>
@@ -6160,25 +6208,29 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>深圳市汇淼淼贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D277" s="4" t="inlineStr"/>
+          <t>永安期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>深圳市真利视界科技有限公司</t>
+          <t>永康市浩资建筑材料厂</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -6188,7 +6240,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr"/>
@@ -6196,7 +6248,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>深圳市鼎泉盛世投资管理有限公司</t>
+          <t>汇丰前海证券有限责任公司</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -6206,41 +6258,37 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>基金</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>私募基金</t>
+          <t>外资券商</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>混沌天成期货股份有限公司上海分公司</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C280" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>期货公司分公司</t>
-        </is>
-      </c>
+          <t>汕头市诚兴塑化有限公司</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>湖南中升物贸有限责任公司</t>
+          <t>江山市永丰化建有限公司</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -6258,25 +6306,29 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>潍坊方程式生物化工有限公司</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D282" s="4" t="inlineStr"/>
+          <t>江海汇鑫期货有限公司</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>烟台东诚果业有限公司</t>
+          <t>江西中啟建设工程有限公司</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -6286,7 +6338,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr"/>
@@ -6294,7 +6346,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>牧原食品集团股份有限公司</t>
+          <t>江西国元农业发展集团有限公司</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -6312,131 +6364,115 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>物产中大期货有限公司</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C285" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D285" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>江西状元郎食品集团有限公司</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>王斌华</t>
-        </is>
-      </c>
-      <c r="B286" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C286" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D286" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河北卓峰化肥有限公司</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>王绎翔</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C287" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D287" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河北古月坊农业科技有限公司</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>百万期货</t>
-        </is>
-      </c>
-      <c r="B288" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C288" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D288" s="6" t="inlineStr"/>
+          <t>河南君友商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>石景涛</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C289" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河南省冠林贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>红期分享测试</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C290" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D290" s="6" t="inlineStr"/>
+          <t>河南省才聚万锦生猪贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>绵阳市乐事多食品有限公司</t>
+          <t>河南金之晟养殖有限公司</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -6446,7 +6482,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr"/>
@@ -6454,29 +6490,25 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>胡洋洋</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C292" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>河南鑫诺农业发展有限公司</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>芜湖中铸材料科技有限公司</t>
+          <t>泉州市润心塑胶科技有限公司</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -6494,7 +6526,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>苏州万家鲜食品有限公司</t>
+          <t>泰安市泰山区海阔饲料销售中心</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -6504,7 +6536,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr"/>
@@ -6512,51 +6544,43 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>苏州创元和赢资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D295" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>济宁市明辰木业有限公司</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>苏州创元投资发展（集团）有限公司</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C296" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D296" s="3" t="inlineStr">
-        <is>
-          <t>私募投资集团</t>
-        </is>
-      </c>
+          <t>浙商中拓集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>苏豪弘业期货股份有限公司</t>
+          <t>浙商期货有限公司上海分公司</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -6571,14 +6595,14 @@
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>蔚县怡洲商贸有限公司</t>
+          <t>浙江华道律师事务所</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -6588,7 +6612,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr"/>
@@ -6596,47 +6620,47 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>融创智富（深圳）资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C299" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D299" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>浙江卓诗尼鞋业有限公司</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>衡水宝泰机械配件制造有限公司</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D300" s="4" t="inlineStr"/>
+          <t>浙江南华资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>券商私募（另类投资）</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>许昌市同庆纺织实业有限公司</t>
+          <t>浙江响农农副产品有限公司</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -6646,7 +6670,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr"/>
@@ -6654,29 +6678,29 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>诸城市大科建材营销店（个体工商户）</t>
-        </is>
-      </c>
-      <c r="B302" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C302" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D302" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>浙江新世纪期货有限公司</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>谷实生物科技（天津）有限公司</t>
+          <t>浙江旺璐物资有限公司</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -6686,7 +6710,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr"/>
@@ -6694,65 +6718,65 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>账号已注销</t>
-        </is>
-      </c>
-      <c r="B304" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C304" s="6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D304" s="6" t="inlineStr"/>
+          <t>浙江杭实善成实业有限公司</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>贵州百农汇农业集团有限公司</t>
-        </is>
-      </c>
-      <c r="B305" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>农林牧渔业</t>
-        </is>
-      </c>
-      <c r="D305" s="4" t="inlineStr"/>
+          <t>海南佳岳私募证券基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>贵阳新泰投资有限公司</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C306" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D306" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
-        </is>
-      </c>
+          <t>海南农垦草畜猪业有限公司</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>赣州盈实信息科技有限公司</t>
+          <t>海宁帕提时尚服饰有限公司</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -6762,7 +6786,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr"/>
@@ -6770,25 +6794,29 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>路源（大连）石化产品有限公司</t>
-        </is>
-      </c>
-      <c r="B308" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C308" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="inlineStr"/>
+          <t>海通期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>邢台麦之多商贸有限公司</t>
+          <t>淄博市多盈数据智能有限公司</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -6798,7 +6826,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr"/>
@@ -6806,29 +6834,29 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>郁卫华</t>
-        </is>
-      </c>
-      <c r="B310" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C310" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D310" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
+          <t>深圳中盈蓝景私募证券基金管理有限公司</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>郑州市赛迪商贸有限公司</t>
+          <t>深圳市乐禾荷文化实业有限公司</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -6838,7 +6866,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>贸易业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr"/>
@@ -6846,25 +6874,29 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>重庆日邦商贸有限公司</t>
-        </is>
-      </c>
-      <c r="B312" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D312" s="4" t="inlineStr"/>
+          <t>深圳市滨利投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>重庆泰戈新能源发展有限公司</t>
+          <t>深圳市真利视界科技有限公司</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -6874,7 +6906,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr"/>
@@ -6882,25 +6914,29 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>重庆航铝物资有限责任公司</t>
-        </is>
-      </c>
-      <c r="B314" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C314" s="4" t="inlineStr">
-        <is>
-          <t>贸易业</t>
-        </is>
-      </c>
-      <c r="D314" s="4" t="inlineStr"/>
+          <t>深圳市鼎泉盛世投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>银河期货有限公司</t>
+          <t>混沌天成期货股份有限公司上海分公司</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
@@ -6915,58 +6951,50 @@
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>期货公司</t>
+          <t>期货公司分公司</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>长安期货有限公司</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C316" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>清河县仟昌商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>长江期货股份有限公司</t>
-        </is>
-      </c>
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C317" s="3" t="inlineStr">
-        <is>
-          <t>期货</t>
-        </is>
-      </c>
-      <c r="D317" s="3" t="inlineStr">
-        <is>
-          <t>期货公司</t>
-        </is>
-      </c>
+          <t>湖南中升物贸有限责任公司</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>长沙市玉阅咨询服务有限公司</t>
+          <t>湖南金润通贸易发展有限公司</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -6976,7 +7004,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>贸易业</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr"/>
@@ -6984,7 +7012,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>阿克苏市恒鑫顺调料批发部</t>
+          <t>潍坊方程式生物化工有限公司</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -6994,7 +7022,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr"/>
@@ -7002,29 +7030,25 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>陈荣跃</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
-        <is>
-          <t>个人客户</t>
-        </is>
-      </c>
+          <t>烟台东诚果业有限公司</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>陕西亿佳农牧科技有限公司</t>
+          <t>烟台仕源建筑劳务有限公司</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -7034,7 +7058,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr"/>
@@ -7042,7 +7066,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>隆昌博文视光眼镜有限责任公司</t>
+          <t>牧原食品集团股份有限公司</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -7052,7 +7076,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>服务业</t>
+          <t>农林牧渔业</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr"/>
@@ -7060,25 +7084,29 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>青岛信达新材料有限公司</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D323" s="4" t="inlineStr"/>
+          <t>物产中大期货有限公司</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>青岛柏霖农业科技发展有限公司</t>
+          <t>甘肃宇航电力科技有限公司</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -7088,7 +7116,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr"/>
@@ -7096,43 +7124,47 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>青岛金月亮建设工程有限公司</t>
-        </is>
-      </c>
-      <c r="B325" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C325" s="4" t="inlineStr">
-        <is>
-          <t>建筑业</t>
-        </is>
-      </c>
-      <c r="D325" s="4" t="inlineStr"/>
+          <t>甬兴证券有限公司</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>证券公司</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>黄梅县泰源棉业有限公司</t>
-        </is>
-      </c>
-      <c r="B326" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C326" s="4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="D326" s="4" t="inlineStr"/>
+          <t>百万期货</t>
+        </is>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C326" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D326" s="6" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>黑山县贺兴养殖专业合作社</t>
+          <t>石家庄市北为商业管理有限公司</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
@@ -7142,7 +7174,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>农林牧渔业</t>
+          <t>服务业</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr"/>
@@ -7150,45 +7182,893 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>黑龙江优上家族投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="B328" s="3" t="inlineStr">
-        <is>
-          <t>金融客户</t>
-        </is>
-      </c>
-      <c r="C328" s="3" t="inlineStr">
-        <is>
-          <t>基金</t>
-        </is>
-      </c>
-      <c r="D328" s="3" t="inlineStr">
-        <is>
-          <t>私募基金</t>
+          <t>石景涛</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
+          <t>磐启国际贸易（北京）有限公司</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>红期分享测试</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>绵阳市乐事多食品有限公司</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>胡洋洋</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>芜湖中铸材料科技有限公司</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>苏州创元和赢资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>苏州创元投资发展（集团）有限公司</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>私募投资集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>苏豪弘业期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>营销管理部</t>
+        </is>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C337" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D337" s="6" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>营销管理部</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D338" s="6" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>融创智富（深圳）资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>衡水宝泰机械配件制造有限公司</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>许昌市同庆纺织实业有限公司</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>许昌市建安区天运生猪养殖场</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>诸城市大科建材营销店（个体工商户）</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>谷实生物科技（天津）有限公司</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>账号已注销</t>
+        </is>
+      </c>
+      <c r="B345" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C345" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D345" s="6" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>贵州百农汇农业集团有限公司</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>赖永春</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>赣州盈实信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>路源（大连）石化产品有限公司</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>辽宁昊瑞实商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>邢台麦之多商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>邯郸市瑞霞贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B352" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>郁卫华</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>郑州市赛迪商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>重庆日邦商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>重庆航铝物资有限责任公司</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>银河期货有限公司</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>长江期货股份有限公司</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>期货</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>期货公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>陈泓霖</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>陈荣跃</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>陕西亿佳农牧科技有限公司</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>陕西宏展农业开发有限公司</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D362" s="4" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>隆昌博文视光眼镜有限责任公司</t>
+        </is>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>青岛信达新材料有限公司</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>青岛柏霖农业科技发展有限公司</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>青岛金月亮建设工程有限公司</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>建筑业</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>青岛锦记实业有限公司</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>贸易业</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>马玉坤</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+      <c r="D368" s="5" t="inlineStr">
+        <is>
+          <t>个人客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>鸿霆科技（海南）有限公司</t>
+        </is>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>服务业</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>黑山县贺兴养殖专业合作社</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>农林牧渔业</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江优上家族投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>金融客户</t>
+        </is>
+      </c>
+      <c r="C371" s="3" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>私募基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
           <t>鼎成纺织（南通）有限公司</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
-        <is>
-          <t>产业客户</t>
-        </is>
-      </c>
-      <c r="C329" s="4" t="inlineStr">
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr">
         <is>
           <t>制造业</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr"/>
+      <c r="D372" s="4" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>龙口市昱阳食品有限公司</t>
+        </is>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>产业客户</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D373" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D329"/>
+  <autoFilter ref="A1:D373"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7231,7 +8111,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
@@ -7241,7 +8121,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -7251,7 +8131,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -7261,7 +8141,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
